--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21069100</v>
+        <v>21655000</v>
       </c>
       <c r="E8" s="3">
-        <v>18712000</v>
+        <v>19232300</v>
       </c>
       <c r="F8" s="3">
-        <v>20355800</v>
+        <v>20921800</v>
       </c>
       <c r="G8" s="3">
-        <v>17580500</v>
+        <v>18069400</v>
       </c>
       <c r="H8" s="3">
-        <v>19507200</v>
+        <v>20049700</v>
       </c>
       <c r="I8" s="3">
-        <v>17509800</v>
+        <v>17996800</v>
       </c>
       <c r="J8" s="3">
-        <v>18527100</v>
+        <v>19042300</v>
       </c>
       <c r="K8" s="3">
         <v>17610400</v>
@@ -823,25 +823,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19425300</v>
+        <v>19965500</v>
       </c>
       <c r="E9" s="3">
-        <v>17136400</v>
+        <v>17613000</v>
       </c>
       <c r="F9" s="3">
-        <v>18836000</v>
+        <v>19359800</v>
       </c>
       <c r="G9" s="3">
-        <v>16204700</v>
+        <v>16655400</v>
       </c>
       <c r="H9" s="3">
-        <v>17958900</v>
+        <v>18458300</v>
       </c>
       <c r="I9" s="3">
-        <v>16408200</v>
+        <v>16864500</v>
       </c>
       <c r="J9" s="3">
-        <v>16926700</v>
+        <v>17397500</v>
       </c>
       <c r="K9" s="3">
         <v>16130200</v>
@@ -885,25 +885,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1643800</v>
+        <v>1689500</v>
       </c>
       <c r="E10" s="3">
-        <v>1575600</v>
+        <v>1619400</v>
       </c>
       <c r="F10" s="3">
-        <v>1519700</v>
+        <v>1562000</v>
       </c>
       <c r="G10" s="3">
-        <v>1375800</v>
+        <v>1414100</v>
       </c>
       <c r="H10" s="3">
-        <v>1548300</v>
+        <v>1591300</v>
       </c>
       <c r="I10" s="3">
-        <v>1101700</v>
+        <v>1132300</v>
       </c>
       <c r="J10" s="3">
-        <v>1600400</v>
+        <v>1644900</v>
       </c>
       <c r="K10" s="3">
         <v>1480200</v>
@@ -1095,25 +1095,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>140200</v>
+        <v>144100</v>
       </c>
       <c r="E14" s="3">
-        <v>584300</v>
+        <v>600600</v>
       </c>
       <c r="F14" s="3">
-        <v>-7400</v>
+        <v>-7700</v>
       </c>
       <c r="G14" s="3">
-        <v>27300</v>
+        <v>28100</v>
       </c>
       <c r="H14" s="3">
-        <v>-138900</v>
+        <v>-142800</v>
       </c>
       <c r="I14" s="3">
-        <v>106700</v>
+        <v>109700</v>
       </c>
       <c r="J14" s="3">
-        <v>540900</v>
+        <v>555900</v>
       </c>
       <c r="K14" s="3">
         <v>140700</v>
@@ -1240,25 +1240,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20531900</v>
+        <v>21102900</v>
       </c>
       <c r="E17" s="3">
-        <v>18616400</v>
+        <v>19134200</v>
       </c>
       <c r="F17" s="3">
-        <v>19695800</v>
+        <v>20243500</v>
       </c>
       <c r="G17" s="3">
-        <v>16988800</v>
+        <v>17461200</v>
       </c>
       <c r="H17" s="3">
-        <v>18676000</v>
+        <v>19195400</v>
       </c>
       <c r="I17" s="3">
-        <v>17365900</v>
+        <v>17848800</v>
       </c>
       <c r="J17" s="3">
-        <v>18453900</v>
+        <v>18967100</v>
       </c>
       <c r="K17" s="3">
         <v>17069300</v>
@@ -1302,25 +1302,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>537200</v>
+        <v>552100</v>
       </c>
       <c r="E18" s="3">
-        <v>95500</v>
+        <v>98200</v>
       </c>
       <c r="F18" s="3">
-        <v>660000</v>
+        <v>678400</v>
       </c>
       <c r="G18" s="3">
-        <v>591800</v>
+        <v>608200</v>
       </c>
       <c r="H18" s="3">
-        <v>831200</v>
+        <v>854300</v>
       </c>
       <c r="I18" s="3">
-        <v>143900</v>
+        <v>147900</v>
       </c>
       <c r="J18" s="3">
-        <v>73200</v>
+        <v>75200</v>
       </c>
       <c r="K18" s="3">
         <v>541100</v>
@@ -1388,25 +1388,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>14900</v>
+        <v>15300</v>
       </c>
       <c r="E20" s="3">
-        <v>16100</v>
+        <v>16600</v>
       </c>
       <c r="F20" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="G20" s="3">
-        <v>-29800</v>
+        <v>-30600</v>
       </c>
       <c r="H20" s="3">
-        <v>34700</v>
+        <v>35700</v>
       </c>
       <c r="I20" s="3">
-        <v>9900</v>
+        <v>10200</v>
       </c>
       <c r="J20" s="3">
-        <v>-6200</v>
+        <v>-6400</v>
       </c>
       <c r="K20" s="3">
         <v>-10100</v>
@@ -1450,25 +1450,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1334900</v>
+        <v>1372000</v>
       </c>
       <c r="E21" s="3">
-        <v>803900</v>
+        <v>826300</v>
       </c>
       <c r="F21" s="3">
-        <v>1472600</v>
+        <v>1513500</v>
       </c>
       <c r="G21" s="3">
-        <v>1258000</v>
+        <v>1293000</v>
       </c>
       <c r="H21" s="3">
-        <v>1683500</v>
+        <v>1730300</v>
       </c>
       <c r="I21" s="3">
-        <v>883300</v>
+        <v>907900</v>
       </c>
       <c r="J21" s="3">
-        <v>887000</v>
+        <v>911700</v>
       </c>
       <c r="K21" s="3">
         <v>1277400</v>
@@ -1512,25 +1512,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>210900</v>
+        <v>216800</v>
       </c>
       <c r="E22" s="3">
-        <v>172400</v>
+        <v>177200</v>
       </c>
       <c r="F22" s="3">
-        <v>199700</v>
+        <v>205300</v>
       </c>
       <c r="G22" s="3">
-        <v>173700</v>
+        <v>178500</v>
       </c>
       <c r="H22" s="3">
-        <v>212100</v>
+        <v>218000</v>
       </c>
       <c r="I22" s="3">
-        <v>186100</v>
+        <v>191300</v>
       </c>
       <c r="J22" s="3">
-        <v>237000</v>
+        <v>243500</v>
       </c>
       <c r="K22" s="3">
         <v>219200</v>
@@ -1574,25 +1574,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>341200</v>
+        <v>350700</v>
       </c>
       <c r="E23" s="3">
-        <v>-60800</v>
+        <v>-62500</v>
       </c>
       <c r="F23" s="3">
-        <v>466500</v>
+        <v>479400</v>
       </c>
       <c r="G23" s="3">
-        <v>388300</v>
+        <v>399100</v>
       </c>
       <c r="H23" s="3">
-        <v>653800</v>
+        <v>672000</v>
       </c>
       <c r="I23" s="3">
-        <v>-32300</v>
+        <v>-33200</v>
       </c>
       <c r="J23" s="3">
-        <v>-170000</v>
+        <v>-174700</v>
       </c>
       <c r="K23" s="3">
         <v>311800</v>
@@ -1636,25 +1636,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>148900</v>
+        <v>153000</v>
       </c>
       <c r="E24" s="3">
-        <v>36000</v>
+        <v>37000</v>
       </c>
       <c r="F24" s="3">
-        <v>112900</v>
+        <v>116000</v>
       </c>
       <c r="G24" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="H24" s="3">
-        <v>184800</v>
+        <v>190000</v>
       </c>
       <c r="I24" s="3">
-        <v>-6200</v>
+        <v>-6400</v>
       </c>
       <c r="J24" s="3">
-        <v>52100</v>
+        <v>53600</v>
       </c>
       <c r="K24" s="3">
         <v>71000</v>
@@ -1760,25 +1760,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>192300</v>
+        <v>197600</v>
       </c>
       <c r="E26" s="3">
-        <v>-96800</v>
+        <v>-99500</v>
       </c>
       <c r="F26" s="3">
-        <v>353600</v>
+        <v>363400</v>
       </c>
       <c r="G26" s="3">
-        <v>357300</v>
+        <v>367200</v>
       </c>
       <c r="H26" s="3">
-        <v>468900</v>
+        <v>482000</v>
       </c>
       <c r="I26" s="3">
-        <v>-26100</v>
+        <v>-26800</v>
       </c>
       <c r="J26" s="3">
-        <v>-222100</v>
+        <v>-228200</v>
       </c>
       <c r="K26" s="3">
         <v>240800</v>
@@ -1822,25 +1822,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>192300</v>
+        <v>197600</v>
       </c>
       <c r="E27" s="3">
-        <v>-96800</v>
+        <v>-99500</v>
       </c>
       <c r="F27" s="3">
-        <v>353600</v>
+        <v>363400</v>
       </c>
       <c r="G27" s="3">
-        <v>357300</v>
+        <v>367200</v>
       </c>
       <c r="H27" s="3">
-        <v>468900</v>
+        <v>482000</v>
       </c>
       <c r="I27" s="3">
-        <v>-29800</v>
+        <v>-30600</v>
       </c>
       <c r="J27" s="3">
-        <v>-227000</v>
+        <v>-233300</v>
       </c>
       <c r="K27" s="3">
         <v>225600</v>
@@ -2132,25 +2132,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-14900</v>
+        <v>-15300</v>
       </c>
       <c r="E32" s="3">
-        <v>-16100</v>
+        <v>-16600</v>
       </c>
       <c r="F32" s="3">
-        <v>-6200</v>
+        <v>-6400</v>
       </c>
       <c r="G32" s="3">
-        <v>29800</v>
+        <v>30600</v>
       </c>
       <c r="H32" s="3">
-        <v>-34700</v>
+        <v>-35700</v>
       </c>
       <c r="I32" s="3">
-        <v>-9900</v>
+        <v>-10200</v>
       </c>
       <c r="J32" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="K32" s="3">
         <v>10100</v>
@@ -2194,25 +2194,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>192300</v>
+        <v>197600</v>
       </c>
       <c r="E33" s="3">
-        <v>-96800</v>
+        <v>-99500</v>
       </c>
       <c r="F33" s="3">
-        <v>353600</v>
+        <v>363400</v>
       </c>
       <c r="G33" s="3">
-        <v>357300</v>
+        <v>367200</v>
       </c>
       <c r="H33" s="3">
-        <v>468900</v>
+        <v>482000</v>
       </c>
       <c r="I33" s="3">
-        <v>-29800</v>
+        <v>-30600</v>
       </c>
       <c r="J33" s="3">
-        <v>-227000</v>
+        <v>-233300</v>
       </c>
       <c r="K33" s="3">
         <v>225600</v>
@@ -2318,25 +2318,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>192300</v>
+        <v>197600</v>
       </c>
       <c r="E35" s="3">
-        <v>-96800</v>
+        <v>-99500</v>
       </c>
       <c r="F35" s="3">
-        <v>353600</v>
+        <v>363400</v>
       </c>
       <c r="G35" s="3">
-        <v>357300</v>
+        <v>367200</v>
       </c>
       <c r="H35" s="3">
-        <v>468900</v>
+        <v>482000</v>
       </c>
       <c r="I35" s="3">
-        <v>-29800</v>
+        <v>-30600</v>
       </c>
       <c r="J35" s="3">
-        <v>-227000</v>
+        <v>-233300</v>
       </c>
       <c r="K35" s="3">
         <v>225600</v>
@@ -2495,25 +2495,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1414300</v>
+        <v>1453600</v>
       </c>
       <c r="E41" s="3">
-        <v>1208300</v>
+        <v>1241900</v>
       </c>
       <c r="F41" s="3">
-        <v>1473800</v>
+        <v>1514800</v>
       </c>
       <c r="G41" s="3">
-        <v>733200</v>
+        <v>753600</v>
       </c>
       <c r="H41" s="3">
-        <v>1348500</v>
+        <v>1386000</v>
       </c>
       <c r="I41" s="3">
-        <v>897000</v>
+        <v>921900</v>
       </c>
       <c r="J41" s="3">
-        <v>2054400</v>
+        <v>2111600</v>
       </c>
       <c r="K41" s="3">
         <v>2173400</v>
@@ -2557,25 +2557,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1194700</v>
+        <v>1227900</v>
       </c>
       <c r="E42" s="3">
-        <v>1040900</v>
+        <v>1069800</v>
       </c>
       <c r="F42" s="3">
-        <v>1133900</v>
+        <v>1165400</v>
       </c>
       <c r="G42" s="3">
-        <v>533500</v>
+        <v>548300</v>
       </c>
       <c r="H42" s="3">
-        <v>820000</v>
+        <v>842800</v>
       </c>
       <c r="I42" s="3">
-        <v>1168600</v>
+        <v>1201100</v>
       </c>
       <c r="J42" s="3">
-        <v>586800</v>
+        <v>603100</v>
       </c>
       <c r="K42" s="3">
         <v>449900</v>
@@ -2619,25 +2619,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4940100</v>
+        <v>5077400</v>
       </c>
       <c r="E43" s="3">
-        <v>5100100</v>
+        <v>5241900</v>
       </c>
       <c r="F43" s="3">
-        <v>4966100</v>
+        <v>5104200</v>
       </c>
       <c r="G43" s="3">
-        <v>4771300</v>
+        <v>4904000</v>
       </c>
       <c r="H43" s="3">
-        <v>8294700</v>
+        <v>8525300</v>
       </c>
       <c r="I43" s="3">
-        <v>8658100</v>
+        <v>8898900</v>
       </c>
       <c r="J43" s="3">
-        <v>9314400</v>
+        <v>9573500</v>
       </c>
       <c r="K43" s="3">
         <v>11042000</v>
@@ -2681,25 +2681,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2713200</v>
+        <v>2788600</v>
       </c>
       <c r="E44" s="3">
-        <v>2355900</v>
+        <v>2421400</v>
       </c>
       <c r="F44" s="3">
-        <v>2346000</v>
+        <v>2411200</v>
       </c>
       <c r="G44" s="3">
-        <v>2229400</v>
+        <v>2291400</v>
       </c>
       <c r="H44" s="3">
-        <v>2086700</v>
+        <v>2144700</v>
       </c>
       <c r="I44" s="3">
-        <v>2016000</v>
+        <v>2072000</v>
       </c>
       <c r="J44" s="3">
-        <v>2028400</v>
+        <v>2084800</v>
       </c>
       <c r="K44" s="3">
         <v>2195000</v>
@@ -2743,25 +2743,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>132700</v>
+        <v>136400</v>
       </c>
       <c r="E45" s="3">
-        <v>86800</v>
+        <v>89300</v>
       </c>
       <c r="F45" s="3">
-        <v>138900</v>
+        <v>142800</v>
       </c>
       <c r="G45" s="3">
-        <v>96800</v>
+        <v>99500</v>
       </c>
       <c r="H45" s="3">
-        <v>24800</v>
+        <v>25500</v>
       </c>
       <c r="I45" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="J45" s="3">
-        <v>34700</v>
+        <v>35700</v>
       </c>
       <c r="K45" s="3">
         <v>15200</v>
@@ -2805,25 +2805,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10395000</v>
+        <v>10684100</v>
       </c>
       <c r="E46" s="3">
-        <v>9792100</v>
+        <v>10064400</v>
       </c>
       <c r="F46" s="3">
-        <v>10058800</v>
+        <v>10338500</v>
       </c>
       <c r="G46" s="3">
-        <v>8364100</v>
+        <v>8596700</v>
       </c>
       <c r="H46" s="3">
-        <v>8886400</v>
+        <v>9133500</v>
       </c>
       <c r="I46" s="3">
-        <v>8866600</v>
+        <v>9113100</v>
       </c>
       <c r="J46" s="3">
-        <v>9825600</v>
+        <v>10098800</v>
       </c>
       <c r="K46" s="3">
         <v>9608700</v>
@@ -2867,25 +2867,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2790100</v>
+        <v>2867700</v>
       </c>
       <c r="E47" s="3">
-        <v>3077900</v>
+        <v>3163500</v>
       </c>
       <c r="F47" s="3">
-        <v>2903000</v>
+        <v>2983700</v>
       </c>
       <c r="G47" s="3">
-        <v>3347100</v>
+        <v>3440200</v>
       </c>
       <c r="H47" s="3">
-        <v>3390600</v>
+        <v>3484800</v>
       </c>
       <c r="I47" s="3">
-        <v>6660800</v>
+        <v>6846000</v>
       </c>
       <c r="J47" s="3">
-        <v>8118500</v>
+        <v>8344300</v>
       </c>
       <c r="K47" s="3">
         <v>10049700</v>
@@ -2929,25 +2929,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16681100</v>
+        <v>17145000</v>
       </c>
       <c r="E48" s="3">
-        <v>16805200</v>
+        <v>17272500</v>
       </c>
       <c r="F48" s="3">
-        <v>17031000</v>
+        <v>17504600</v>
       </c>
       <c r="G48" s="3">
-        <v>17321300</v>
+        <v>17802900</v>
       </c>
       <c r="H48" s="3">
-        <v>16920500</v>
+        <v>17391100</v>
       </c>
       <c r="I48" s="3">
-        <v>27195200</v>
+        <v>27951500</v>
       </c>
       <c r="J48" s="3">
-        <v>27635600</v>
+        <v>28404100</v>
       </c>
       <c r="K48" s="3">
         <v>28750000</v>
@@ -2991,25 +2991,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1251800</v>
+        <v>1286600</v>
       </c>
       <c r="E49" s="3">
-        <v>1270400</v>
+        <v>1305700</v>
       </c>
       <c r="F49" s="3">
-        <v>1266700</v>
+        <v>1301900</v>
       </c>
       <c r="G49" s="3">
-        <v>1248000</v>
+        <v>1282800</v>
       </c>
       <c r="H49" s="3">
-        <v>1241800</v>
+        <v>1276400</v>
       </c>
       <c r="I49" s="3">
-        <v>1133900</v>
+        <v>1165400</v>
       </c>
       <c r="J49" s="3">
-        <v>1064400</v>
+        <v>1094000</v>
       </c>
       <c r="K49" s="3">
         <v>1234400</v>
@@ -3177,25 +3177,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1347300</v>
+        <v>1384800</v>
       </c>
       <c r="E52" s="3">
-        <v>1506100</v>
+        <v>1548000</v>
       </c>
       <c r="F52" s="3">
-        <v>2353400</v>
+        <v>2418900</v>
       </c>
       <c r="G52" s="3">
-        <v>3106500</v>
+        <v>3192900</v>
       </c>
       <c r="H52" s="3">
-        <v>1414300</v>
+        <v>1453600</v>
       </c>
       <c r="I52" s="3">
-        <v>962700</v>
+        <v>989500</v>
       </c>
       <c r="J52" s="3">
-        <v>1262900</v>
+        <v>1298100</v>
       </c>
       <c r="K52" s="3">
         <v>1430800</v>
@@ -3301,25 +3301,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32465300</v>
+        <v>33368100</v>
       </c>
       <c r="E54" s="3">
-        <v>32451600</v>
+        <v>33354100</v>
       </c>
       <c r="F54" s="3">
-        <v>33612800</v>
+        <v>34547600</v>
       </c>
       <c r="G54" s="3">
-        <v>33387000</v>
+        <v>34315500</v>
       </c>
       <c r="H54" s="3">
-        <v>31853600</v>
+        <v>32739500</v>
       </c>
       <c r="I54" s="3">
-        <v>31337600</v>
+        <v>32209000</v>
       </c>
       <c r="J54" s="3">
-        <v>33599200</v>
+        <v>34533500</v>
       </c>
       <c r="K54" s="3">
         <v>35404600</v>
@@ -3411,25 +3411,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6547900</v>
+        <v>6730000</v>
       </c>
       <c r="E57" s="3">
-        <v>6000800</v>
+        <v>6167700</v>
       </c>
       <c r="F57" s="3">
-        <v>6160800</v>
+        <v>6332100</v>
       </c>
       <c r="G57" s="3">
-        <v>5639800</v>
+        <v>5796600</v>
       </c>
       <c r="H57" s="3">
-        <v>5660900</v>
+        <v>5818300</v>
       </c>
       <c r="I57" s="3">
-        <v>5567800</v>
+        <v>5722600</v>
       </c>
       <c r="J57" s="3">
-        <v>5833300</v>
+        <v>5995500</v>
       </c>
       <c r="K57" s="3">
         <v>5417700</v>
@@ -3473,25 +3473,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>666200</v>
+        <v>684700</v>
       </c>
       <c r="E58" s="3">
-        <v>1967600</v>
+        <v>2022300</v>
       </c>
       <c r="F58" s="3">
-        <v>1970100</v>
+        <v>2024900</v>
       </c>
       <c r="G58" s="3">
-        <v>719500</v>
+        <v>739600</v>
       </c>
       <c r="H58" s="3">
-        <v>1016100</v>
+        <v>1044300</v>
       </c>
       <c r="I58" s="3">
-        <v>1091700</v>
+        <v>1122100</v>
       </c>
       <c r="J58" s="3">
-        <v>1749200</v>
+        <v>1797900</v>
       </c>
       <c r="K58" s="3">
         <v>707200</v>
@@ -3535,25 +3535,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7169400</v>
+        <v>7368800</v>
       </c>
       <c r="E59" s="3">
-        <v>6440000</v>
+        <v>6619000</v>
       </c>
       <c r="F59" s="3">
-        <v>6258800</v>
+        <v>6432900</v>
       </c>
       <c r="G59" s="3">
-        <v>5882900</v>
+        <v>6046500</v>
       </c>
       <c r="H59" s="3">
-        <v>6577700</v>
+        <v>6760600</v>
       </c>
       <c r="I59" s="3">
-        <v>8015500</v>
+        <v>8238400</v>
       </c>
       <c r="J59" s="3">
-        <v>7578800</v>
+        <v>7789600</v>
       </c>
       <c r="K59" s="3">
         <v>9146100</v>
@@ -3597,25 +3597,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14383500</v>
+        <v>14783500</v>
       </c>
       <c r="E60" s="3">
-        <v>14408300</v>
+        <v>14809000</v>
       </c>
       <c r="F60" s="3">
-        <v>14389700</v>
+        <v>14789900</v>
       </c>
       <c r="G60" s="3">
-        <v>12242200</v>
+        <v>12582700</v>
       </c>
       <c r="H60" s="3">
-        <v>13254600</v>
+        <v>13623200</v>
       </c>
       <c r="I60" s="3">
-        <v>14675100</v>
+        <v>15083200</v>
       </c>
       <c r="J60" s="3">
-        <v>15161400</v>
+        <v>15583000</v>
       </c>
       <c r="K60" s="3">
         <v>15271000</v>
@@ -3659,25 +3659,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7555300</v>
+        <v>7765400</v>
       </c>
       <c r="E61" s="3">
-        <v>6896500</v>
+        <v>7088300</v>
       </c>
       <c r="F61" s="3">
-        <v>7045400</v>
+        <v>7241300</v>
       </c>
       <c r="G61" s="3">
-        <v>8438600</v>
+        <v>8673200</v>
       </c>
       <c r="H61" s="3">
-        <v>8046500</v>
+        <v>8270300</v>
       </c>
       <c r="I61" s="3">
-        <v>7515600</v>
+        <v>7724600</v>
       </c>
       <c r="J61" s="3">
-        <v>7618500</v>
+        <v>7830400</v>
       </c>
       <c r="K61" s="3">
         <v>8252700</v>
@@ -3721,25 +3721,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1565600</v>
+        <v>1609200</v>
       </c>
       <c r="E62" s="3">
-        <v>2148700</v>
+        <v>2208500</v>
       </c>
       <c r="F62" s="3">
-        <v>2341000</v>
+        <v>2406100</v>
       </c>
       <c r="G62" s="3">
-        <v>2256700</v>
+        <v>2319400</v>
       </c>
       <c r="H62" s="3">
-        <v>1667400</v>
+        <v>1713700</v>
       </c>
       <c r="I62" s="3">
-        <v>833700</v>
+        <v>856900</v>
       </c>
       <c r="J62" s="3">
-        <v>1903100</v>
+        <v>1956000</v>
       </c>
       <c r="K62" s="3">
         <v>2007400</v>
@@ -3969,25 +3969,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23504400</v>
+        <v>24158000</v>
       </c>
       <c r="E66" s="3">
-        <v>23453500</v>
+        <v>24105800</v>
       </c>
       <c r="F66" s="3">
-        <v>23776100</v>
+        <v>24437300</v>
       </c>
       <c r="G66" s="3">
-        <v>22937500</v>
+        <v>23575300</v>
       </c>
       <c r="H66" s="3">
-        <v>22968500</v>
+        <v>23607200</v>
       </c>
       <c r="I66" s="3">
-        <v>23024300</v>
+        <v>23664600</v>
       </c>
       <c r="J66" s="3">
-        <v>24683000</v>
+        <v>25369400</v>
       </c>
       <c r="K66" s="3">
         <v>25531000</v>
@@ -4303,25 +4303,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6350600</v>
+        <v>6527200</v>
       </c>
       <c r="E72" s="3">
-        <v>6405200</v>
+        <v>6583300</v>
       </c>
       <c r="F72" s="3">
-        <v>7258800</v>
+        <v>7460600</v>
       </c>
       <c r="G72" s="3">
-        <v>7876600</v>
+        <v>8095600</v>
       </c>
       <c r="H72" s="3">
-        <v>6324600</v>
+        <v>6500500</v>
       </c>
       <c r="I72" s="3">
-        <v>5760100</v>
+        <v>5920300</v>
       </c>
       <c r="J72" s="3">
-        <v>6377900</v>
+        <v>6555300</v>
       </c>
       <c r="K72" s="3">
         <v>6972700</v>
@@ -4551,25 +4551,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8960900</v>
+        <v>9210000</v>
       </c>
       <c r="E76" s="3">
-        <v>8998100</v>
+        <v>9248300</v>
       </c>
       <c r="F76" s="3">
-        <v>9836700</v>
+        <v>10110300</v>
       </c>
       <c r="G76" s="3">
-        <v>10449600</v>
+        <v>10740200</v>
       </c>
       <c r="H76" s="3">
-        <v>8885200</v>
+        <v>9132300</v>
       </c>
       <c r="I76" s="3">
-        <v>8313300</v>
+        <v>8544400</v>
       </c>
       <c r="J76" s="3">
-        <v>8916200</v>
+        <v>9164100</v>
       </c>
       <c r="K76" s="3">
         <v>9873500</v>
@@ -4742,25 +4742,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>192300</v>
+        <v>197600</v>
       </c>
       <c r="E81" s="3">
-        <v>-96800</v>
+        <v>-99500</v>
       </c>
       <c r="F81" s="3">
-        <v>353600</v>
+        <v>363400</v>
       </c>
       <c r="G81" s="3">
-        <v>357300</v>
+        <v>367200</v>
       </c>
       <c r="H81" s="3">
-        <v>468900</v>
+        <v>482000</v>
       </c>
       <c r="I81" s="3">
-        <v>-29800</v>
+        <v>-30600</v>
       </c>
       <c r="J81" s="3">
-        <v>-227000</v>
+        <v>-233300</v>
       </c>
       <c r="K81" s="3">
         <v>225600</v>
@@ -4828,25 +4828,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>782800</v>
+        <v>804600</v>
       </c>
       <c r="E83" s="3">
-        <v>692300</v>
+        <v>711500</v>
       </c>
       <c r="F83" s="3">
-        <v>806400</v>
+        <v>828800</v>
       </c>
       <c r="G83" s="3">
-        <v>696000</v>
+        <v>715300</v>
       </c>
       <c r="H83" s="3">
-        <v>817600</v>
+        <v>840300</v>
       </c>
       <c r="I83" s="3">
-        <v>729500</v>
+        <v>749800</v>
       </c>
       <c r="J83" s="3">
-        <v>820000</v>
+        <v>842800</v>
       </c>
       <c r="K83" s="3">
         <v>746400</v>
@@ -5200,25 +5200,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1592900</v>
+        <v>1637200</v>
       </c>
       <c r="E89" s="3">
-        <v>765500</v>
+        <v>786700</v>
       </c>
       <c r="F89" s="3">
-        <v>1945300</v>
+        <v>1999400</v>
       </c>
       <c r="G89" s="3">
-        <v>119100</v>
+        <v>122400</v>
       </c>
       <c r="H89" s="3">
-        <v>1132700</v>
+        <v>1164200</v>
       </c>
       <c r="I89" s="3">
-        <v>1032200</v>
+        <v>1060900</v>
       </c>
       <c r="J89" s="3">
-        <v>1874500</v>
+        <v>1926700</v>
       </c>
       <c r="K89" s="3">
         <v>441000</v>
@@ -5472,25 +5472,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-766700</v>
+        <v>-788000</v>
       </c>
       <c r="E94" s="3">
-        <v>-539700</v>
+        <v>-554700</v>
       </c>
       <c r="F94" s="3">
-        <v>-358500</v>
+        <v>-368500</v>
       </c>
       <c r="G94" s="3">
-        <v>-456500</v>
+        <v>-469200</v>
       </c>
       <c r="H94" s="3">
-        <v>-348600</v>
+        <v>-358300</v>
       </c>
       <c r="I94" s="3">
-        <v>-359800</v>
+        <v>-369800</v>
       </c>
       <c r="J94" s="3">
-        <v>-326300</v>
+        <v>-335400</v>
       </c>
       <c r="K94" s="3">
         <v>-422000</v>
@@ -5558,7 +5558,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-266700</v>
+        <v>-274100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -5570,10 +5570,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-5000</v>
+        <v>-5100</v>
       </c>
       <c r="I96" s="3">
-        <v>-28500</v>
+        <v>-29300</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -5806,25 +5806,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>99200</v>
+        <v>102000</v>
       </c>
       <c r="E100" s="3">
-        <v>-545900</v>
+        <v>-561000</v>
       </c>
       <c r="F100" s="3">
-        <v>-645100</v>
+        <v>-663100</v>
       </c>
       <c r="G100" s="3">
-        <v>-428000</v>
+        <v>-439900</v>
       </c>
       <c r="H100" s="3">
-        <v>-834900</v>
+        <v>-858100</v>
       </c>
       <c r="I100" s="3">
-        <v>-643900</v>
+        <v>-661800</v>
       </c>
       <c r="J100" s="3">
-        <v>-978800</v>
+        <v>-1006100</v>
       </c>
       <c r="K100" s="3">
         <v>-618400</v>
@@ -5930,25 +5930,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>925500</v>
+        <v>951200</v>
       </c>
       <c r="E102" s="3">
-        <v>-320100</v>
+        <v>-329000</v>
       </c>
       <c r="F102" s="3">
-        <v>941600</v>
+        <v>967800</v>
       </c>
       <c r="G102" s="3">
-        <v>-765500</v>
+        <v>-786700</v>
       </c>
       <c r="H102" s="3">
-        <v>-50900</v>
+        <v>-52300</v>
       </c>
       <c r="I102" s="3">
-        <v>28500</v>
+        <v>29300</v>
       </c>
       <c r="J102" s="3">
-        <v>569400</v>
+        <v>585300</v>
       </c>
       <c r="K102" s="3">
         <v>-599400</v>

--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>JSAIY</t>
   </si>
@@ -656,293 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45353</v>
+      </c>
+      <c r="E7" s="2">
         <v>45185</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44989</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44821</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44625</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44457</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44261</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44093</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43897</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43729</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43533</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43365</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43169</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43001</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42805</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42637</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42441</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42273</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42077</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21655000</v>
+        <v>20111600</v>
       </c>
       <c r="E8" s="3">
-        <v>19232300</v>
+        <v>21731600</v>
       </c>
       <c r="F8" s="3">
-        <v>20921800</v>
+        <v>19300400</v>
       </c>
       <c r="G8" s="3">
-        <v>18069400</v>
+        <v>20995800</v>
       </c>
       <c r="H8" s="3">
-        <v>20049700</v>
+        <v>18133400</v>
       </c>
       <c r="I8" s="3">
-        <v>17996800</v>
+        <v>20120600</v>
       </c>
       <c r="J8" s="3">
+        <v>18060400</v>
+      </c>
+      <c r="K8" s="3">
         <v>19042300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17610400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18732400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16418700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18453400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18836700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20722900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17939000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16343700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14460900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16198200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14626900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16679800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>19965500</v>
+        <v>18573500</v>
       </c>
       <c r="E9" s="3">
-        <v>17613000</v>
+        <v>20036100</v>
       </c>
       <c r="F9" s="3">
-        <v>19359800</v>
+        <v>17675300</v>
       </c>
       <c r="G9" s="3">
-        <v>16655400</v>
+        <v>19428300</v>
       </c>
       <c r="H9" s="3">
-        <v>18458300</v>
+        <v>16714300</v>
       </c>
       <c r="I9" s="3">
-        <v>16864500</v>
+        <v>18523600</v>
       </c>
       <c r="J9" s="3">
+        <v>16924100</v>
+      </c>
+      <c r="K9" s="3">
         <v>17397500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16130200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17335200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15099700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17022500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17614700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19327600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16791200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15354700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13549200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15210900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13693300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16022700</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1689500</v>
+        <v>1538100</v>
       </c>
       <c r="E10" s="3">
-        <v>1619400</v>
+        <v>1695500</v>
       </c>
       <c r="F10" s="3">
-        <v>1562000</v>
+        <v>1625100</v>
       </c>
       <c r="G10" s="3">
-        <v>1414100</v>
+        <v>1567500</v>
       </c>
       <c r="H10" s="3">
-        <v>1591300</v>
+        <v>1419100</v>
       </c>
       <c r="I10" s="3">
-        <v>1132300</v>
+        <v>1597000</v>
       </c>
       <c r="J10" s="3">
+        <v>1136300</v>
+      </c>
+      <c r="K10" s="3">
         <v>1644900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1480200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1397100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1318900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1430900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1222000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1395300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1147800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>989000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>911700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>987400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>933600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>657100</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -965,8 +978,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,8 +1041,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1089,46 +1106,49 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>144100</v>
+        <v>436300</v>
       </c>
       <c r="E14" s="3">
-        <v>600600</v>
+        <v>144600</v>
       </c>
       <c r="F14" s="3">
+        <v>602700</v>
+      </c>
+      <c r="G14" s="3">
         <v>-7700</v>
       </c>
-      <c r="G14" s="3">
-        <v>28100</v>
-      </c>
       <c r="H14" s="3">
-        <v>-142800</v>
+        <v>28200</v>
       </c>
       <c r="I14" s="3">
-        <v>109700</v>
+        <v>-143300</v>
       </c>
       <c r="J14" s="3">
+        <v>110000</v>
+      </c>
+      <c r="K14" s="3">
         <v>555900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>140700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>277900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>30800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-17100</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1139,8 +1159,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1151,8 +1171,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1213,8 +1236,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1234,132 +1260,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21102900</v>
+        <v>19935000</v>
       </c>
       <c r="E17" s="3">
-        <v>19134200</v>
+        <v>21177500</v>
       </c>
       <c r="F17" s="3">
-        <v>20243500</v>
+        <v>19201800</v>
       </c>
       <c r="G17" s="3">
-        <v>17461200</v>
+        <v>20315100</v>
       </c>
       <c r="H17" s="3">
-        <v>19195400</v>
+        <v>17523000</v>
       </c>
       <c r="I17" s="3">
-        <v>17848800</v>
+        <v>19263200</v>
       </c>
       <c r="J17" s="3">
+        <v>17912000</v>
+      </c>
+      <c r="K17" s="3">
         <v>18967100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17069300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18419700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16096900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18063100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18516200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20322400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17694600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15752900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14090500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15646500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14212100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16987900</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>552100</v>
+        <v>176600</v>
       </c>
       <c r="E18" s="3">
-        <v>98200</v>
+        <v>554100</v>
       </c>
       <c r="F18" s="3">
-        <v>678400</v>
+        <v>98500</v>
       </c>
       <c r="G18" s="3">
-        <v>608200</v>
+        <v>680800</v>
       </c>
       <c r="H18" s="3">
-        <v>854300</v>
+        <v>610400</v>
       </c>
       <c r="I18" s="3">
-        <v>147900</v>
+        <v>857300</v>
       </c>
       <c r="J18" s="3">
+        <v>148400</v>
+      </c>
+      <c r="K18" s="3">
         <v>75200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>541100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>312700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>321700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>390400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>320500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>244300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>590800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>370400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>551700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>414800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1382,318 +1415,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15300</v>
+        <v>23000</v>
       </c>
       <c r="E20" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F20" s="3">
         <v>16600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-30600</v>
-      </c>
       <c r="H20" s="3">
-        <v>35700</v>
+        <v>-30700</v>
       </c>
       <c r="I20" s="3">
+        <v>35800</v>
+      </c>
+      <c r="J20" s="3">
         <v>10200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-43400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-29700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-24800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-26100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-48700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1372000</v>
+        <v>899600</v>
       </c>
       <c r="E21" s="3">
-        <v>826300</v>
+        <v>1376900</v>
       </c>
       <c r="F21" s="3">
-        <v>1513500</v>
+        <v>829200</v>
       </c>
       <c r="G21" s="3">
-        <v>1293000</v>
+        <v>1518900</v>
       </c>
       <c r="H21" s="3">
-        <v>1730300</v>
+        <v>1297500</v>
       </c>
       <c r="I21" s="3">
-        <v>907900</v>
+        <v>1736400</v>
       </c>
       <c r="J21" s="3">
+        <v>911100</v>
+      </c>
+      <c r="K21" s="3">
         <v>911700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1277400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1096900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1019700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1232100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>831900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>904300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>639300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>983800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>705600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>927400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>709700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>119800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>216800</v>
+        <v>197100</v>
       </c>
       <c r="E22" s="3">
-        <v>177200</v>
+        <v>217500</v>
       </c>
       <c r="F22" s="3">
-        <v>205300</v>
+        <v>177900</v>
       </c>
       <c r="G22" s="3">
-        <v>178500</v>
+        <v>206000</v>
       </c>
       <c r="H22" s="3">
-        <v>218000</v>
+        <v>179100</v>
       </c>
       <c r="I22" s="3">
-        <v>191300</v>
+        <v>218800</v>
       </c>
       <c r="J22" s="3">
+        <v>191900</v>
+      </c>
+      <c r="K22" s="3">
         <v>243500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>219200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>258100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>220000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>270800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>70900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>80700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>68700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>80200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>73000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>83500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>79000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>350700</v>
+        <v>2600</v>
       </c>
       <c r="E23" s="3">
-        <v>-62500</v>
+        <v>351900</v>
       </c>
       <c r="F23" s="3">
-        <v>479400</v>
+        <v>-62700</v>
       </c>
       <c r="G23" s="3">
-        <v>399100</v>
+        <v>481100</v>
       </c>
       <c r="H23" s="3">
-        <v>672000</v>
+        <v>400500</v>
       </c>
       <c r="I23" s="3">
-        <v>-33200</v>
+        <v>674400</v>
       </c>
       <c r="J23" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-174700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>311800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>112400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>130500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>257800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>311300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>173000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>480900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>272600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>442200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>287100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-381900</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>153000</v>
+        <v>25600</v>
       </c>
       <c r="E24" s="3">
-        <v>37000</v>
+        <v>153600</v>
       </c>
       <c r="F24" s="3">
-        <v>116000</v>
+        <v>37100</v>
       </c>
       <c r="G24" s="3">
-        <v>31900</v>
+        <v>116400</v>
       </c>
       <c r="H24" s="3">
-        <v>190000</v>
+        <v>32000</v>
       </c>
       <c r="I24" s="3">
+        <v>190700</v>
+      </c>
+      <c r="J24" s="3">
         <v>-6400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>53600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>71000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-19500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>62700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>70000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>94400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>97800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>52700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>71100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,132 +1803,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>197600</v>
+        <v>-23000</v>
       </c>
       <c r="E26" s="3">
-        <v>-99500</v>
+        <v>198300</v>
       </c>
       <c r="F26" s="3">
-        <v>363400</v>
+        <v>-99800</v>
       </c>
       <c r="G26" s="3">
-        <v>367200</v>
+        <v>364700</v>
       </c>
       <c r="H26" s="3">
-        <v>482000</v>
+        <v>368500</v>
       </c>
       <c r="I26" s="3">
-        <v>-26800</v>
+        <v>483700</v>
       </c>
       <c r="J26" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-228200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>240800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-47200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>74500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>150000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>195000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>234900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>103000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>386600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>270000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>344300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>234400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>197600</v>
+        <v>-23000</v>
       </c>
       <c r="E27" s="3">
-        <v>-99500</v>
+        <v>198300</v>
       </c>
       <c r="F27" s="3">
-        <v>363400</v>
+        <v>-99800</v>
       </c>
       <c r="G27" s="3">
-        <v>367200</v>
+        <v>364700</v>
       </c>
       <c r="H27" s="3">
-        <v>482000</v>
+        <v>368500</v>
       </c>
       <c r="I27" s="3">
-        <v>-30600</v>
+        <v>483700</v>
       </c>
       <c r="J27" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-233300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>225600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-60800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>65100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>137800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>184100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>220800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>92500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>373600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>256900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>341700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>234400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1940,8 +1998,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2002,8 +2063,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,8 +2128,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2126,132 +2193,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15300</v>
+        <v>-23000</v>
       </c>
       <c r="E32" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-16600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6400</v>
       </c>
-      <c r="G32" s="3">
-        <v>30600</v>
-      </c>
       <c r="H32" s="3">
-        <v>-35700</v>
+        <v>30700</v>
       </c>
       <c r="I32" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="J32" s="3">
         <v>-10200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>43400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>29700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>24800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>26100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>48700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>197600</v>
+        <v>-23000</v>
       </c>
       <c r="E33" s="3">
-        <v>-99500</v>
+        <v>198300</v>
       </c>
       <c r="F33" s="3">
-        <v>363400</v>
+        <v>-99800</v>
       </c>
       <c r="G33" s="3">
-        <v>367200</v>
+        <v>364700</v>
       </c>
       <c r="H33" s="3">
-        <v>482000</v>
+        <v>368500</v>
       </c>
       <c r="I33" s="3">
-        <v>-30600</v>
+        <v>483700</v>
       </c>
       <c r="J33" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="K33" s="3">
         <v>-233300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>225600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-60800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>65100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>137800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>184100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>220800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>92500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>373600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>256900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>341700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>234400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2312,137 +2388,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>197600</v>
+        <v>-23000</v>
       </c>
       <c r="E35" s="3">
-        <v>-99500</v>
+        <v>198300</v>
       </c>
       <c r="F35" s="3">
-        <v>363400</v>
+        <v>-99800</v>
       </c>
       <c r="G35" s="3">
-        <v>367200</v>
+        <v>364700</v>
       </c>
       <c r="H35" s="3">
-        <v>482000</v>
+        <v>368500</v>
       </c>
       <c r="I35" s="3">
-        <v>-30600</v>
+        <v>483700</v>
       </c>
       <c r="J35" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="K35" s="3">
         <v>-233300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>225600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-60800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>65100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>137800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>184100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>220800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>92500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>373600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>256900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>341700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>234400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45353</v>
+      </c>
+      <c r="E38" s="2">
         <v>45185</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44989</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44821</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44625</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44457</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44261</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44093</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43897</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43729</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43533</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43365</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43169</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43001</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42805</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42637</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42441</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42273</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42077</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2465,8 +2550,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2489,566 +2575,594 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1453600</v>
+        <v>1408900</v>
       </c>
       <c r="E41" s="3">
-        <v>1241900</v>
+        <v>1458800</v>
       </c>
       <c r="F41" s="3">
-        <v>1514800</v>
+        <v>1246300</v>
       </c>
       <c r="G41" s="3">
-        <v>753600</v>
+        <v>1520200</v>
       </c>
       <c r="H41" s="3">
-        <v>1386000</v>
+        <v>756200</v>
       </c>
       <c r="I41" s="3">
-        <v>921900</v>
+        <v>1390900</v>
       </c>
       <c r="J41" s="3">
+        <v>925200</v>
+      </c>
+      <c r="K41" s="3">
         <v>2111600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2173400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1372300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>961700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1095500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1427900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1542500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1112100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1383300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1113900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1494700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1692100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1865900</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1227900</v>
+        <v>1155500</v>
       </c>
       <c r="E42" s="3">
-        <v>1069800</v>
+        <v>1232300</v>
       </c>
       <c r="F42" s="3">
-        <v>1165400</v>
+        <v>1073600</v>
       </c>
       <c r="G42" s="3">
-        <v>548300</v>
+        <v>1169600</v>
       </c>
       <c r="H42" s="3">
-        <v>842800</v>
+        <v>550200</v>
       </c>
       <c r="I42" s="3">
-        <v>1201100</v>
+        <v>845800</v>
       </c>
       <c r="J42" s="3">
+        <v>1205400</v>
+      </c>
+      <c r="K42" s="3">
         <v>603100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>449900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>675000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>613900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1119900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1208300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>536300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>450400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>309000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>439600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>156500</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5077400</v>
+        <v>4647500</v>
       </c>
       <c r="E43" s="3">
-        <v>5241900</v>
+        <v>5095400</v>
       </c>
       <c r="F43" s="3">
-        <v>5104200</v>
+        <v>5260500</v>
       </c>
       <c r="G43" s="3">
-        <v>4904000</v>
+        <v>5122300</v>
       </c>
       <c r="H43" s="3">
-        <v>8525300</v>
+        <v>4921400</v>
       </c>
       <c r="I43" s="3">
-        <v>8898900</v>
+        <v>8555500</v>
       </c>
       <c r="J43" s="3">
+        <v>8930400</v>
+      </c>
+      <c r="K43" s="3">
         <v>9573500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11042000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5584800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5048600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5044300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5597000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5115600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4305800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4140900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2873400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2986900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2725800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2561200</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2788600</v>
+        <v>2465800</v>
       </c>
       <c r="E44" s="3">
-        <v>2421400</v>
+        <v>2798500</v>
       </c>
       <c r="F44" s="3">
-        <v>2411200</v>
+        <v>2430000</v>
       </c>
       <c r="G44" s="3">
-        <v>2291400</v>
+        <v>2419700</v>
       </c>
       <c r="H44" s="3">
-        <v>2144700</v>
+        <v>2299500</v>
       </c>
       <c r="I44" s="3">
-        <v>2072000</v>
+        <v>2152300</v>
       </c>
       <c r="J44" s="3">
+        <v>2079400</v>
+      </c>
+      <c r="K44" s="3">
         <v>2084800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2195000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2423300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2281800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2292200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2468500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2728300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2344400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2460200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1262600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1321300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1312800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1389200</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>136400</v>
+        <v>10200</v>
       </c>
       <c r="E45" s="3">
-        <v>89300</v>
+        <v>136900</v>
       </c>
       <c r="F45" s="3">
-        <v>142800</v>
+        <v>89600</v>
       </c>
       <c r="G45" s="3">
-        <v>99500</v>
+        <v>143300</v>
       </c>
       <c r="H45" s="3">
+        <v>99800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>25600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>35700</v>
+      </c>
+      <c r="L45" s="3">
+        <v>15200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>50900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>24800</v>
+      </c>
+      <c r="O45" s="3">
+        <v>57300</v>
+      </c>
+      <c r="P45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>25500</v>
       </c>
-      <c r="I45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>35700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>15200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>50900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>24800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>57300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>13600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>25500</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>124200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>175800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>66500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>90900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10684100</v>
+        <v>9687900</v>
       </c>
       <c r="E46" s="3">
-        <v>10064400</v>
+        <v>10721900</v>
       </c>
       <c r="F46" s="3">
-        <v>10338500</v>
+        <v>10100000</v>
       </c>
       <c r="G46" s="3">
-        <v>8596700</v>
+        <v>10375100</v>
       </c>
       <c r="H46" s="3">
-        <v>9133500</v>
+        <v>8627100</v>
       </c>
       <c r="I46" s="3">
-        <v>9113100</v>
+        <v>9165800</v>
       </c>
       <c r="J46" s="3">
+        <v>9145400</v>
+      </c>
+      <c r="K46" s="3">
         <v>10098800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9608700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10106300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8930900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9609200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10715300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9948200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8336800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8469200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5755900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6018100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5821500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5878200</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2867700</v>
+        <v>2991700</v>
       </c>
       <c r="E47" s="3">
-        <v>3163500</v>
+        <v>2877800</v>
       </c>
       <c r="F47" s="3">
-        <v>2983700</v>
+        <v>3174700</v>
       </c>
       <c r="G47" s="3">
-        <v>3440200</v>
+        <v>2994300</v>
       </c>
       <c r="H47" s="3">
-        <v>3484800</v>
+        <v>3452400</v>
       </c>
       <c r="I47" s="3">
-        <v>6846000</v>
+        <v>3497200</v>
       </c>
       <c r="J47" s="3">
+        <v>6870200</v>
+      </c>
+      <c r="K47" s="3">
         <v>8344300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10049700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5629500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5034400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4342800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4293200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4044400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3509300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3243700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3155100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2870800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2683600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2766600</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17145000</v>
+        <v>17374500</v>
       </c>
       <c r="E48" s="3">
-        <v>17272500</v>
+        <v>17205600</v>
       </c>
       <c r="F48" s="3">
-        <v>17504600</v>
+        <v>17333600</v>
       </c>
       <c r="G48" s="3">
-        <v>17802900</v>
+        <v>17566500</v>
       </c>
       <c r="H48" s="3">
-        <v>17391100</v>
+        <v>17865900</v>
       </c>
       <c r="I48" s="3">
-        <v>27951500</v>
+        <v>17452600</v>
       </c>
       <c r="J48" s="3">
+        <v>28050300</v>
+      </c>
+      <c r="K48" s="3">
         <v>28404100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28750000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17149100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16780600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17492100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13498800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14078900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13215800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12974600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12735300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12722200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12704400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12620100</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1286600</v>
+        <v>1031400</v>
       </c>
       <c r="E49" s="3">
-        <v>1305700</v>
+        <v>1291100</v>
       </c>
       <c r="F49" s="3">
-        <v>1301900</v>
+        <v>1310300</v>
       </c>
       <c r="G49" s="3">
-        <v>1282800</v>
+        <v>1306500</v>
       </c>
       <c r="H49" s="3">
-        <v>1276400</v>
+        <v>1287300</v>
       </c>
       <c r="I49" s="3">
-        <v>1165400</v>
+        <v>1280900</v>
       </c>
       <c r="J49" s="3">
+        <v>1169600</v>
+      </c>
+      <c r="K49" s="3">
         <v>1094000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1234400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1250700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1233800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1282100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1462000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1178800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1060600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1027800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>429100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>448700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>428000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>399000</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3223,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3171,70 +3288,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1384800</v>
+        <v>982700</v>
       </c>
       <c r="E52" s="3">
-        <v>1548000</v>
+        <v>1389700</v>
       </c>
       <c r="F52" s="3">
-        <v>2418900</v>
+        <v>1553400</v>
       </c>
       <c r="G52" s="3">
-        <v>3192900</v>
+        <v>2427400</v>
       </c>
       <c r="H52" s="3">
-        <v>1453600</v>
+        <v>3204100</v>
       </c>
       <c r="I52" s="3">
-        <v>989500</v>
+        <v>1458800</v>
       </c>
       <c r="J52" s="3">
+        <v>993000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1298100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1430800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1730900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1154500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>356200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>60800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>62600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>138300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3295,70 +3418,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>33368100</v>
+        <v>32068300</v>
       </c>
       <c r="E54" s="3">
-        <v>33354100</v>
+        <v>33486100</v>
       </c>
       <c r="F54" s="3">
-        <v>34547600</v>
+        <v>33472000</v>
       </c>
       <c r="G54" s="3">
-        <v>34315500</v>
+        <v>34669800</v>
       </c>
       <c r="H54" s="3">
-        <v>32739500</v>
+        <v>34436900</v>
       </c>
       <c r="I54" s="3">
-        <v>32209000</v>
+        <v>32855300</v>
       </c>
       <c r="J54" s="3">
+        <v>32322900</v>
+      </c>
+      <c r="K54" s="3">
         <v>34533500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35404600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35866600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33134200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33082500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30004700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29263100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26149000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>25776000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22138100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22131500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21775800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21715200</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3381,8 +3510,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3405,380 +3535,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6730000</v>
+        <v>6514500</v>
       </c>
       <c r="E57" s="3">
-        <v>6167700</v>
+        <v>6753800</v>
       </c>
       <c r="F57" s="3">
-        <v>6332100</v>
+        <v>6189500</v>
       </c>
       <c r="G57" s="3">
-        <v>5796600</v>
+        <v>6354500</v>
       </c>
       <c r="H57" s="3">
-        <v>5818300</v>
+        <v>5817100</v>
       </c>
       <c r="I57" s="3">
-        <v>5722600</v>
+        <v>5838900</v>
       </c>
       <c r="J57" s="3">
+        <v>5742900</v>
+      </c>
+      <c r="K57" s="3">
         <v>5995500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5417700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5844200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5172800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5833600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5894300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5920800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4941100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5511200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8151900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8526300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8369500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8190400</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>684700</v>
+        <v>742200</v>
       </c>
       <c r="E58" s="3">
-        <v>2022300</v>
+        <v>687200</v>
       </c>
       <c r="F58" s="3">
-        <v>2024900</v>
+        <v>2029500</v>
       </c>
       <c r="G58" s="3">
-        <v>739600</v>
+        <v>2032000</v>
       </c>
       <c r="H58" s="3">
-        <v>1044300</v>
+        <v>742200</v>
       </c>
       <c r="I58" s="3">
-        <v>1122100</v>
+        <v>1048000</v>
       </c>
       <c r="J58" s="3">
+        <v>1126100</v>
+      </c>
+      <c r="K58" s="3">
         <v>1797900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>707200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1279300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1595700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>933200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>870100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>984900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>454400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>586900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>290900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>230900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>342400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>492500</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7368800</v>
+        <v>7397400</v>
       </c>
       <c r="E59" s="3">
-        <v>6619000</v>
+        <v>7394900</v>
       </c>
       <c r="F59" s="3">
-        <v>6432900</v>
+        <v>6642500</v>
       </c>
       <c r="G59" s="3">
-        <v>6046500</v>
+        <v>6455600</v>
       </c>
       <c r="H59" s="3">
-        <v>6760600</v>
+        <v>6067900</v>
       </c>
       <c r="I59" s="3">
-        <v>8238400</v>
+        <v>6784500</v>
       </c>
       <c r="J59" s="3">
+        <v>8267600</v>
+      </c>
+      <c r="K59" s="3">
         <v>7789600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9146100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8557800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7247600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6802200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7285400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7275100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6172100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5257900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>322200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>277800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>404300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>358200</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14783500</v>
+        <v>14654100</v>
       </c>
       <c r="E60" s="3">
-        <v>14809000</v>
+        <v>14835800</v>
       </c>
       <c r="F60" s="3">
-        <v>14789900</v>
+        <v>14861400</v>
       </c>
       <c r="G60" s="3">
-        <v>12582700</v>
+        <v>14842200</v>
       </c>
       <c r="H60" s="3">
-        <v>13623200</v>
+        <v>12627200</v>
       </c>
       <c r="I60" s="3">
-        <v>15083200</v>
+        <v>13671400</v>
       </c>
       <c r="J60" s="3">
+        <v>15136500</v>
+      </c>
+      <c r="K60" s="3">
         <v>15583000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15271000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15681200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14016200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13568900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14049800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14180800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11340300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11062600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8765000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9035000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9116100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9041100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7765400</v>
+        <v>7638000</v>
       </c>
       <c r="E61" s="3">
-        <v>7088300</v>
+        <v>7792800</v>
       </c>
       <c r="F61" s="3">
-        <v>7241300</v>
+        <v>7113400</v>
       </c>
       <c r="G61" s="3">
-        <v>8673200</v>
+        <v>7266900</v>
       </c>
       <c r="H61" s="3">
-        <v>8270300</v>
+        <v>8703900</v>
       </c>
       <c r="I61" s="3">
-        <v>7724600</v>
+        <v>8299600</v>
       </c>
       <c r="J61" s="3">
+        <v>7751900</v>
+      </c>
+      <c r="K61" s="3">
         <v>7830400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8252700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7771100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7265400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8113600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2184800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2042000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2693100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2731700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2856400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3018200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3299900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3443400</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1609200</v>
+        <v>987900</v>
       </c>
       <c r="E62" s="3">
-        <v>2208500</v>
+        <v>1614900</v>
       </c>
       <c r="F62" s="3">
-        <v>2406100</v>
+        <v>2216300</v>
       </c>
       <c r="G62" s="3">
-        <v>2319400</v>
+        <v>2414600</v>
       </c>
       <c r="H62" s="3">
-        <v>1713700</v>
+        <v>2327600</v>
       </c>
       <c r="I62" s="3">
-        <v>856900</v>
+        <v>1719800</v>
       </c>
       <c r="J62" s="3">
+        <v>859900</v>
+      </c>
+      <c r="K62" s="3">
         <v>1956000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2007400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2604400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2647300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2648400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3663100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3223600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3039100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3586300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2214700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1977300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2066000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1966000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3839,8 +3988,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3901,8 +4053,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3963,70 +4118,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>24158000</v>
+        <v>23279900</v>
       </c>
       <c r="E66" s="3">
-        <v>24105800</v>
+        <v>24243500</v>
       </c>
       <c r="F66" s="3">
-        <v>24437300</v>
+        <v>24191000</v>
       </c>
       <c r="G66" s="3">
-        <v>23575300</v>
+        <v>24523700</v>
       </c>
       <c r="H66" s="3">
-        <v>23607200</v>
+        <v>23658700</v>
       </c>
       <c r="I66" s="3">
-        <v>23664600</v>
+        <v>23690700</v>
       </c>
       <c r="J66" s="3">
+        <v>23748300</v>
+      </c>
+      <c r="K66" s="3">
         <v>25369400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25531000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26056800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>23928900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>24330900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19897700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19446400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17072500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17380500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13836100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14030500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14482100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14450500</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4049,8 +4210,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4111,8 +4273,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4173,8 +4338,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4235,8 +4403,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4297,70 +4468,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6527200</v>
+        <v>6090900</v>
       </c>
       <c r="E72" s="3">
-        <v>6583300</v>
+        <v>6550300</v>
       </c>
       <c r="F72" s="3">
-        <v>7460600</v>
+        <v>6606600</v>
       </c>
       <c r="G72" s="3">
-        <v>8095600</v>
+        <v>7487000</v>
       </c>
       <c r="H72" s="3">
-        <v>6500500</v>
+        <v>8124200</v>
       </c>
       <c r="I72" s="3">
-        <v>5920300</v>
+        <v>6523500</v>
       </c>
       <c r="J72" s="3">
+        <v>5941200</v>
+      </c>
+      <c r="K72" s="3">
         <v>6555300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6972700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6982000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6516600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5988500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7034400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6639700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6116600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5500900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5484600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5285100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5113100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5098600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4421,8 +4598,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4483,8 +4663,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4545,70 +4728,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9210000</v>
+        <v>8788400</v>
       </c>
       <c r="E76" s="3">
-        <v>9248300</v>
+        <v>9242600</v>
       </c>
       <c r="F76" s="3">
-        <v>10110300</v>
+        <v>9281000</v>
       </c>
       <c r="G76" s="3">
-        <v>10740200</v>
+        <v>10146000</v>
       </c>
       <c r="H76" s="3">
-        <v>9132300</v>
+        <v>10778200</v>
       </c>
       <c r="I76" s="3">
-        <v>8544400</v>
+        <v>9164600</v>
       </c>
       <c r="J76" s="3">
+        <v>8574700</v>
+      </c>
+      <c r="K76" s="3">
         <v>9164100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9873500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9809800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9205300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8751600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10107000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9816600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9076500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8395500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8301900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8101100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7293700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7264700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4669,137 +4858,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45353</v>
+      </c>
+      <c r="E80" s="2">
         <v>45185</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44989</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44821</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44625</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44457</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44261</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44093</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43897</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43729</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43533</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43365</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43169</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43001</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42805</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42637</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42441</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42273</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42077</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>197600</v>
+        <v>-23000</v>
       </c>
       <c r="E81" s="3">
-        <v>-99500</v>
+        <v>198300</v>
       </c>
       <c r="F81" s="3">
-        <v>363400</v>
+        <v>-99800</v>
       </c>
       <c r="G81" s="3">
-        <v>367200</v>
+        <v>364700</v>
       </c>
       <c r="H81" s="3">
-        <v>482000</v>
+        <v>368500</v>
       </c>
       <c r="I81" s="3">
-        <v>-30600</v>
+        <v>483700</v>
       </c>
       <c r="J81" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="K81" s="3">
         <v>-233300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>225600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-60800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>65100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>137800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>184100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>220800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>92500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>373600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>256900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>341700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>234400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4822,70 +5020,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>804600</v>
+        <v>699900</v>
       </c>
       <c r="E83" s="3">
-        <v>711500</v>
+        <v>807400</v>
       </c>
       <c r="F83" s="3">
-        <v>828800</v>
+        <v>714000</v>
       </c>
       <c r="G83" s="3">
-        <v>715300</v>
+        <v>831700</v>
       </c>
       <c r="H83" s="3">
-        <v>840300</v>
+        <v>717900</v>
       </c>
       <c r="I83" s="3">
-        <v>749800</v>
+        <v>843300</v>
       </c>
       <c r="J83" s="3">
+        <v>752400</v>
+      </c>
+      <c r="K83" s="3">
         <v>842800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>746400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>827600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>687300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>830800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>503200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>512300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>397600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>422700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>360000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>401700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>343700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4946,8 +5148,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5008,8 +5213,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5070,8 +5278,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5132,8 +5343,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5194,70 +5408,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1637200</v>
+        <v>871400</v>
       </c>
       <c r="E89" s="3">
-        <v>786700</v>
+        <v>1643000</v>
       </c>
       <c r="F89" s="3">
-        <v>1999400</v>
+        <v>789500</v>
       </c>
       <c r="G89" s="3">
-        <v>122400</v>
+        <v>2006400</v>
       </c>
       <c r="H89" s="3">
-        <v>1164200</v>
+        <v>122800</v>
       </c>
       <c r="I89" s="3">
-        <v>1060900</v>
+        <v>1168300</v>
       </c>
       <c r="J89" s="3">
+        <v>1064600</v>
+      </c>
+      <c r="K89" s="3">
         <v>1926700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>441000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1270600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>105300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1163800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>782800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1119400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>537600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>964400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>189100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>322200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>675500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>524100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5280,70 +5500,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-429000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1130000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-430000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-308000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-375000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-319000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-294000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-301000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-374000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-265000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-282700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-286700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-380500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-399100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-431900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-396900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-373000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-469600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-583300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-771600</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5404,8 +5628,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5466,70 +5693,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-788000</v>
+        <v>-508000</v>
       </c>
       <c r="E94" s="3">
-        <v>-554700</v>
+        <v>-790800</v>
       </c>
       <c r="F94" s="3">
-        <v>-368500</v>
+        <v>-556600</v>
       </c>
       <c r="G94" s="3">
-        <v>-469200</v>
+        <v>-369800</v>
       </c>
       <c r="H94" s="3">
-        <v>-358300</v>
+        <v>-470900</v>
       </c>
       <c r="I94" s="3">
-        <v>-369800</v>
+        <v>-359600</v>
       </c>
       <c r="J94" s="3">
+        <v>-371100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-335400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-422000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-308700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-259800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-261800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-393400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-394900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-583100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-113500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-408200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-454300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-730800</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5552,16 +5785,17 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-274100</v>
+        <v>-116400</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-275100</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -5570,52 +5804,55 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-5100</v>
       </c>
-      <c r="I96" s="3">
-        <v>-29300</v>
-      </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-29400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-24800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-24400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-4100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-25900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>199600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-204800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-126400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5676,8 +5913,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5738,8 +5978,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5800,70 +6043,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>102000</v>
+        <v>-463200</v>
       </c>
       <c r="E100" s="3">
-        <v>-561000</v>
+        <v>102400</v>
       </c>
       <c r="F100" s="3">
-        <v>-663100</v>
+        <v>-563000</v>
       </c>
       <c r="G100" s="3">
-        <v>-439900</v>
+        <v>-665400</v>
       </c>
       <c r="H100" s="3">
-        <v>-858100</v>
+        <v>-441500</v>
       </c>
       <c r="I100" s="3">
-        <v>-661800</v>
+        <v>-861200</v>
       </c>
       <c r="J100" s="3">
+        <v>-664100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1006100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-618400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-724600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-912500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>19100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-365100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-281300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-327100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-233500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>66500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-385800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5924,66 +6173,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>951200</v>
+        <v>-99800</v>
       </c>
       <c r="E102" s="3">
-        <v>-329000</v>
+        <v>954600</v>
       </c>
       <c r="F102" s="3">
-        <v>967800</v>
+        <v>-330100</v>
       </c>
       <c r="G102" s="3">
-        <v>-786700</v>
+        <v>971200</v>
       </c>
       <c r="H102" s="3">
-        <v>-52300</v>
+        <v>-789500</v>
       </c>
       <c r="I102" s="3">
-        <v>29300</v>
+        <v>-52500</v>
       </c>
       <c r="J102" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K102" s="3">
         <v>585300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-599400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>430600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-404600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-324500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>540100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>360900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-138700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>54300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-157800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-164600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-234400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -765,25 +765,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>20111600</v>
+        <v>20623800</v>
       </c>
       <c r="E8" s="3">
-        <v>21731600</v>
+        <v>22285100</v>
       </c>
       <c r="F8" s="3">
-        <v>19300400</v>
+        <v>19791900</v>
       </c>
       <c r="G8" s="3">
-        <v>20995800</v>
+        <v>21530600</v>
       </c>
       <c r="H8" s="3">
-        <v>18133400</v>
+        <v>18595200</v>
       </c>
       <c r="I8" s="3">
-        <v>20120600</v>
+        <v>20633000</v>
       </c>
       <c r="J8" s="3">
-        <v>18060400</v>
+        <v>18520400</v>
       </c>
       <c r="K8" s="3">
         <v>19042300</v>
@@ -830,25 +830,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>18573500</v>
+        <v>19046600</v>
       </c>
       <c r="E9" s="3">
-        <v>20036100</v>
+        <v>20546400</v>
       </c>
       <c r="F9" s="3">
-        <v>17675300</v>
+        <v>18125400</v>
       </c>
       <c r="G9" s="3">
-        <v>19428300</v>
+        <v>19923100</v>
       </c>
       <c r="H9" s="3">
-        <v>16714300</v>
+        <v>17140000</v>
       </c>
       <c r="I9" s="3">
-        <v>18523600</v>
+        <v>18995400</v>
       </c>
       <c r="J9" s="3">
-        <v>16924100</v>
+        <v>17355200</v>
       </c>
       <c r="K9" s="3">
         <v>17397500</v>
@@ -895,25 +895,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1538100</v>
+        <v>1577300</v>
       </c>
       <c r="E10" s="3">
-        <v>1695500</v>
+        <v>1738700</v>
       </c>
       <c r="F10" s="3">
-        <v>1625100</v>
+        <v>1666500</v>
       </c>
       <c r="G10" s="3">
-        <v>1567500</v>
+        <v>1607400</v>
       </c>
       <c r="H10" s="3">
-        <v>1419100</v>
+        <v>1455200</v>
       </c>
       <c r="I10" s="3">
-        <v>1597000</v>
+        <v>1637600</v>
       </c>
       <c r="J10" s="3">
-        <v>1136300</v>
+        <v>1165200</v>
       </c>
       <c r="K10" s="3">
         <v>1644900</v>
@@ -1115,25 +1115,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>436300</v>
+        <v>447500</v>
       </c>
       <c r="E14" s="3">
-        <v>144600</v>
+        <v>148300</v>
       </c>
       <c r="F14" s="3">
-        <v>602700</v>
+        <v>618000</v>
       </c>
       <c r="G14" s="3">
-        <v>-7700</v>
+        <v>-7900</v>
       </c>
       <c r="H14" s="3">
-        <v>28200</v>
+        <v>28900</v>
       </c>
       <c r="I14" s="3">
-        <v>-143300</v>
+        <v>-147000</v>
       </c>
       <c r="J14" s="3">
-        <v>110000</v>
+        <v>112800</v>
       </c>
       <c r="K14" s="3">
         <v>555900</v>
@@ -1267,25 +1267,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19935000</v>
+        <v>20442800</v>
       </c>
       <c r="E17" s="3">
-        <v>21177500</v>
+        <v>21716900</v>
       </c>
       <c r="F17" s="3">
-        <v>19201800</v>
+        <v>19690900</v>
       </c>
       <c r="G17" s="3">
-        <v>20315100</v>
+        <v>20832500</v>
       </c>
       <c r="H17" s="3">
-        <v>17523000</v>
+        <v>17969300</v>
       </c>
       <c r="I17" s="3">
-        <v>19263200</v>
+        <v>19753900</v>
       </c>
       <c r="J17" s="3">
-        <v>17912000</v>
+        <v>18368200</v>
       </c>
       <c r="K17" s="3">
         <v>18967100</v>
@@ -1332,25 +1332,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>176600</v>
+        <v>181100</v>
       </c>
       <c r="E18" s="3">
-        <v>554100</v>
+        <v>568200</v>
       </c>
       <c r="F18" s="3">
-        <v>98500</v>
+        <v>101000</v>
       </c>
       <c r="G18" s="3">
-        <v>680800</v>
+        <v>698100</v>
       </c>
       <c r="H18" s="3">
-        <v>610400</v>
+        <v>625900</v>
       </c>
       <c r="I18" s="3">
-        <v>857300</v>
+        <v>879200</v>
       </c>
       <c r="J18" s="3">
-        <v>148400</v>
+        <v>152200</v>
       </c>
       <c r="K18" s="3">
         <v>75200</v>
@@ -1422,25 +1422,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>23000</v>
+        <v>23600</v>
       </c>
       <c r="E20" s="3">
-        <v>15400</v>
+        <v>15700</v>
       </c>
       <c r="F20" s="3">
-        <v>16600</v>
+        <v>17100</v>
       </c>
       <c r="G20" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="H20" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="I20" s="3">
-        <v>35800</v>
+        <v>36700</v>
       </c>
       <c r="J20" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="K20" s="3">
         <v>-6400</v>
@@ -1487,25 +1487,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>899600</v>
+        <v>922500</v>
       </c>
       <c r="E21" s="3">
-        <v>1376900</v>
+        <v>1411900</v>
       </c>
       <c r="F21" s="3">
-        <v>829200</v>
+        <v>850300</v>
       </c>
       <c r="G21" s="3">
-        <v>1518900</v>
+        <v>1557600</v>
       </c>
       <c r="H21" s="3">
-        <v>1297500</v>
+        <v>1330600</v>
       </c>
       <c r="I21" s="3">
-        <v>1736400</v>
+        <v>1780700</v>
       </c>
       <c r="J21" s="3">
-        <v>911100</v>
+        <v>934300</v>
       </c>
       <c r="K21" s="3">
         <v>911700</v>
@@ -1552,25 +1552,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>197100</v>
+        <v>202100</v>
       </c>
       <c r="E22" s="3">
-        <v>217500</v>
+        <v>223100</v>
       </c>
       <c r="F22" s="3">
-        <v>177900</v>
+        <v>182400</v>
       </c>
       <c r="G22" s="3">
-        <v>206000</v>
+        <v>211300</v>
       </c>
       <c r="H22" s="3">
-        <v>179100</v>
+        <v>183700</v>
       </c>
       <c r="I22" s="3">
-        <v>218800</v>
+        <v>224400</v>
       </c>
       <c r="J22" s="3">
-        <v>191900</v>
+        <v>196800</v>
       </c>
       <c r="K22" s="3">
         <v>243500</v>
@@ -1620,22 +1620,22 @@
         <v>2600</v>
       </c>
       <c r="E23" s="3">
-        <v>351900</v>
+        <v>360900</v>
       </c>
       <c r="F23" s="3">
-        <v>-62700</v>
+        <v>-64300</v>
       </c>
       <c r="G23" s="3">
-        <v>481100</v>
+        <v>493400</v>
       </c>
       <c r="H23" s="3">
-        <v>400500</v>
+        <v>410700</v>
       </c>
       <c r="I23" s="3">
-        <v>674400</v>
+        <v>691500</v>
       </c>
       <c r="J23" s="3">
-        <v>-33300</v>
+        <v>-34100</v>
       </c>
       <c r="K23" s="3">
         <v>-174700</v>
@@ -1682,25 +1682,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>25600</v>
+        <v>26200</v>
       </c>
       <c r="E24" s="3">
-        <v>153600</v>
+        <v>157500</v>
       </c>
       <c r="F24" s="3">
-        <v>37100</v>
+        <v>38100</v>
       </c>
       <c r="G24" s="3">
-        <v>116400</v>
+        <v>119400</v>
       </c>
       <c r="H24" s="3">
-        <v>32000</v>
+        <v>32800</v>
       </c>
       <c r="I24" s="3">
-        <v>190700</v>
+        <v>195500</v>
       </c>
       <c r="J24" s="3">
-        <v>-6400</v>
+        <v>-6600</v>
       </c>
       <c r="K24" s="3">
         <v>53600</v>
@@ -1812,25 +1812,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E26" s="3">
-        <v>198300</v>
+        <v>203400</v>
       </c>
       <c r="F26" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="G26" s="3">
-        <v>364700</v>
+        <v>374000</v>
       </c>
       <c r="H26" s="3">
-        <v>368500</v>
+        <v>377900</v>
       </c>
       <c r="I26" s="3">
-        <v>483700</v>
+        <v>496000</v>
       </c>
       <c r="J26" s="3">
-        <v>-26900</v>
+        <v>-27600</v>
       </c>
       <c r="K26" s="3">
         <v>-228200</v>
@@ -1877,25 +1877,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E27" s="3">
-        <v>198300</v>
+        <v>203400</v>
       </c>
       <c r="F27" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="G27" s="3">
-        <v>364700</v>
+        <v>374000</v>
       </c>
       <c r="H27" s="3">
-        <v>368500</v>
+        <v>377900</v>
       </c>
       <c r="I27" s="3">
-        <v>483700</v>
+        <v>496000</v>
       </c>
       <c r="J27" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="K27" s="3">
         <v>-233300</v>
@@ -2202,25 +2202,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E32" s="3">
-        <v>-15400</v>
+        <v>-15700</v>
       </c>
       <c r="F32" s="3">
-        <v>-16600</v>
+        <v>-17100</v>
       </c>
       <c r="G32" s="3">
-        <v>-6400</v>
+        <v>-6600</v>
       </c>
       <c r="H32" s="3">
-        <v>30700</v>
+        <v>31500</v>
       </c>
       <c r="I32" s="3">
-        <v>-35800</v>
+        <v>-36700</v>
       </c>
       <c r="J32" s="3">
-        <v>-10200</v>
+        <v>-10500</v>
       </c>
       <c r="K32" s="3">
         <v>6400</v>
@@ -2267,25 +2267,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E33" s="3">
-        <v>198300</v>
+        <v>203400</v>
       </c>
       <c r="F33" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="G33" s="3">
-        <v>364700</v>
+        <v>374000</v>
       </c>
       <c r="H33" s="3">
-        <v>368500</v>
+        <v>377900</v>
       </c>
       <c r="I33" s="3">
-        <v>483700</v>
+        <v>496000</v>
       </c>
       <c r="J33" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="K33" s="3">
         <v>-233300</v>
@@ -2397,25 +2397,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E35" s="3">
-        <v>198300</v>
+        <v>203400</v>
       </c>
       <c r="F35" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="G35" s="3">
-        <v>364700</v>
+        <v>374000</v>
       </c>
       <c r="H35" s="3">
-        <v>368500</v>
+        <v>377900</v>
       </c>
       <c r="I35" s="3">
-        <v>483700</v>
+        <v>496000</v>
       </c>
       <c r="J35" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="K35" s="3">
         <v>-233300</v>
@@ -2582,25 +2582,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1408900</v>
+        <v>1444700</v>
       </c>
       <c r="E41" s="3">
-        <v>1458800</v>
+        <v>1495900</v>
       </c>
       <c r="F41" s="3">
-        <v>1246300</v>
+        <v>1278100</v>
       </c>
       <c r="G41" s="3">
-        <v>1520200</v>
+        <v>1558900</v>
       </c>
       <c r="H41" s="3">
-        <v>756200</v>
+        <v>775500</v>
       </c>
       <c r="I41" s="3">
-        <v>1390900</v>
+        <v>1426400</v>
       </c>
       <c r="J41" s="3">
-        <v>925200</v>
+        <v>948700</v>
       </c>
       <c r="K41" s="3">
         <v>2111600</v>
@@ -2647,25 +2647,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1155500</v>
+        <v>1184900</v>
       </c>
       <c r="E42" s="3">
-        <v>1232300</v>
+        <v>1263600</v>
       </c>
       <c r="F42" s="3">
-        <v>1073600</v>
+        <v>1100900</v>
       </c>
       <c r="G42" s="3">
-        <v>1169600</v>
+        <v>1199400</v>
       </c>
       <c r="H42" s="3">
-        <v>550200</v>
+        <v>564200</v>
       </c>
       <c r="I42" s="3">
-        <v>845800</v>
+        <v>867400</v>
       </c>
       <c r="J42" s="3">
-        <v>1205400</v>
+        <v>1236100</v>
       </c>
       <c r="K42" s="3">
         <v>603100</v>
@@ -2712,25 +2712,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4647500</v>
+        <v>4765900</v>
       </c>
       <c r="E43" s="3">
-        <v>5095400</v>
+        <v>5225200</v>
       </c>
       <c r="F43" s="3">
-        <v>5260500</v>
+        <v>5394500</v>
       </c>
       <c r="G43" s="3">
-        <v>5122300</v>
+        <v>5252700</v>
       </c>
       <c r="H43" s="3">
-        <v>4921400</v>
+        <v>5046700</v>
       </c>
       <c r="I43" s="3">
-        <v>8555500</v>
+        <v>8773400</v>
       </c>
       <c r="J43" s="3">
-        <v>8930400</v>
+        <v>9157800</v>
       </c>
       <c r="K43" s="3">
         <v>9573500</v>
@@ -2777,25 +2777,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2465800</v>
+        <v>2528600</v>
       </c>
       <c r="E44" s="3">
-        <v>2798500</v>
+        <v>2869800</v>
       </c>
       <c r="F44" s="3">
-        <v>2430000</v>
+        <v>2491900</v>
       </c>
       <c r="G44" s="3">
-        <v>2419700</v>
+        <v>2481400</v>
       </c>
       <c r="H44" s="3">
-        <v>2299500</v>
+        <v>2358000</v>
       </c>
       <c r="I44" s="3">
-        <v>2152300</v>
+        <v>2207100</v>
       </c>
       <c r="J44" s="3">
-        <v>2079400</v>
+        <v>2132300</v>
       </c>
       <c r="K44" s="3">
         <v>2084800</v>
@@ -2842,25 +2842,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10200</v>
+        <v>10500</v>
       </c>
       <c r="E45" s="3">
-        <v>136900</v>
+        <v>140400</v>
       </c>
       <c r="F45" s="3">
-        <v>89600</v>
+        <v>91900</v>
       </c>
       <c r="G45" s="3">
-        <v>143300</v>
+        <v>147000</v>
       </c>
       <c r="H45" s="3">
-        <v>99800</v>
+        <v>102400</v>
       </c>
       <c r="I45" s="3">
-        <v>25600</v>
+        <v>26200</v>
       </c>
       <c r="J45" s="3">
-        <v>6400</v>
+        <v>6600</v>
       </c>
       <c r="K45" s="3">
         <v>35700</v>
@@ -2907,25 +2907,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9687900</v>
+        <v>9934700</v>
       </c>
       <c r="E46" s="3">
-        <v>10721900</v>
+        <v>10994900</v>
       </c>
       <c r="F46" s="3">
-        <v>10100000</v>
+        <v>10357200</v>
       </c>
       <c r="G46" s="3">
-        <v>10375100</v>
+        <v>10639300</v>
       </c>
       <c r="H46" s="3">
-        <v>8627100</v>
+        <v>8846900</v>
       </c>
       <c r="I46" s="3">
-        <v>9165800</v>
+        <v>9399300</v>
       </c>
       <c r="J46" s="3">
-        <v>9145400</v>
+        <v>9378300</v>
       </c>
       <c r="K46" s="3">
         <v>10098800</v>
@@ -2972,25 +2972,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2991700</v>
+        <v>3067900</v>
       </c>
       <c r="E47" s="3">
-        <v>2877800</v>
+        <v>2951100</v>
       </c>
       <c r="F47" s="3">
-        <v>3174700</v>
+        <v>3255600</v>
       </c>
       <c r="G47" s="3">
-        <v>2994300</v>
+        <v>3070500</v>
       </c>
       <c r="H47" s="3">
-        <v>3452400</v>
+        <v>3540300</v>
       </c>
       <c r="I47" s="3">
-        <v>3497200</v>
+        <v>3586200</v>
       </c>
       <c r="J47" s="3">
-        <v>6870200</v>
+        <v>7045200</v>
       </c>
       <c r="K47" s="3">
         <v>8344300</v>
@@ -3037,25 +3037,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17374500</v>
+        <v>17817100</v>
       </c>
       <c r="E48" s="3">
-        <v>17205600</v>
+        <v>17643800</v>
       </c>
       <c r="F48" s="3">
-        <v>17333600</v>
+        <v>17775100</v>
       </c>
       <c r="G48" s="3">
-        <v>17566500</v>
+        <v>18013900</v>
       </c>
       <c r="H48" s="3">
-        <v>17865900</v>
+        <v>18320900</v>
       </c>
       <c r="I48" s="3">
-        <v>17452600</v>
+        <v>17897100</v>
       </c>
       <c r="J48" s="3">
-        <v>28050300</v>
+        <v>28764700</v>
       </c>
       <c r="K48" s="3">
         <v>28404100</v>
@@ -3102,25 +3102,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1031400</v>
+        <v>1057600</v>
       </c>
       <c r="E49" s="3">
-        <v>1291100</v>
+        <v>1324000</v>
       </c>
       <c r="F49" s="3">
-        <v>1310300</v>
+        <v>1343700</v>
       </c>
       <c r="G49" s="3">
-        <v>1306500</v>
+        <v>1339800</v>
       </c>
       <c r="H49" s="3">
-        <v>1287300</v>
+        <v>1320100</v>
       </c>
       <c r="I49" s="3">
-        <v>1280900</v>
+        <v>1313500</v>
       </c>
       <c r="J49" s="3">
-        <v>1169600</v>
+        <v>1199400</v>
       </c>
       <c r="K49" s="3">
         <v>1094000</v>
@@ -3297,25 +3297,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>982700</v>
+        <v>1007800</v>
       </c>
       <c r="E52" s="3">
-        <v>1389700</v>
+        <v>1425000</v>
       </c>
       <c r="F52" s="3">
-        <v>1553400</v>
+        <v>1593000</v>
       </c>
       <c r="G52" s="3">
-        <v>2427400</v>
+        <v>2489200</v>
       </c>
       <c r="H52" s="3">
-        <v>3204100</v>
+        <v>3285700</v>
       </c>
       <c r="I52" s="3">
-        <v>1458800</v>
+        <v>1495900</v>
       </c>
       <c r="J52" s="3">
-        <v>993000</v>
+        <v>1018300</v>
       </c>
       <c r="K52" s="3">
         <v>1298100</v>
@@ -3427,25 +3427,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32068300</v>
+        <v>32885000</v>
       </c>
       <c r="E54" s="3">
-        <v>33486100</v>
+        <v>34339000</v>
       </c>
       <c r="F54" s="3">
-        <v>33472000</v>
+        <v>34324500</v>
       </c>
       <c r="G54" s="3">
-        <v>34669800</v>
+        <v>35552700</v>
       </c>
       <c r="H54" s="3">
-        <v>34436900</v>
+        <v>35313900</v>
       </c>
       <c r="I54" s="3">
-        <v>32855300</v>
+        <v>33692000</v>
       </c>
       <c r="J54" s="3">
-        <v>32322900</v>
+        <v>33146200</v>
       </c>
       <c r="K54" s="3">
         <v>34533500</v>
@@ -3542,25 +3542,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6514500</v>
+        <v>6680400</v>
       </c>
       <c r="E57" s="3">
-        <v>6753800</v>
+        <v>6925800</v>
       </c>
       <c r="F57" s="3">
-        <v>6189500</v>
+        <v>6347100</v>
       </c>
       <c r="G57" s="3">
-        <v>6354500</v>
+        <v>6516400</v>
       </c>
       <c r="H57" s="3">
-        <v>5817100</v>
+        <v>5965300</v>
       </c>
       <c r="I57" s="3">
-        <v>5838900</v>
+        <v>5987600</v>
       </c>
       <c r="J57" s="3">
-        <v>5742900</v>
+        <v>5889200</v>
       </c>
       <c r="K57" s="3">
         <v>5995500</v>
@@ -3607,25 +3607,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>742200</v>
+        <v>761100</v>
       </c>
       <c r="E58" s="3">
-        <v>687200</v>
+        <v>704700</v>
       </c>
       <c r="F58" s="3">
-        <v>2029500</v>
+        <v>2081100</v>
       </c>
       <c r="G58" s="3">
-        <v>2032000</v>
+        <v>2083800</v>
       </c>
       <c r="H58" s="3">
-        <v>742200</v>
+        <v>761100</v>
       </c>
       <c r="I58" s="3">
-        <v>1048000</v>
+        <v>1074700</v>
       </c>
       <c r="J58" s="3">
-        <v>1126100</v>
+        <v>1154700</v>
       </c>
       <c r="K58" s="3">
         <v>1797900</v>
@@ -3672,25 +3672,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7397400</v>
+        <v>7585800</v>
       </c>
       <c r="E59" s="3">
-        <v>7394900</v>
+        <v>7583200</v>
       </c>
       <c r="F59" s="3">
-        <v>6642500</v>
+        <v>6811600</v>
       </c>
       <c r="G59" s="3">
-        <v>6455600</v>
+        <v>6620000</v>
       </c>
       <c r="H59" s="3">
-        <v>6067900</v>
+        <v>6222500</v>
       </c>
       <c r="I59" s="3">
-        <v>6784500</v>
+        <v>6957300</v>
       </c>
       <c r="J59" s="3">
-        <v>8267600</v>
+        <v>8478100</v>
       </c>
       <c r="K59" s="3">
         <v>7789600</v>
@@ -3737,25 +3737,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>14654100</v>
+        <v>15027300</v>
       </c>
       <c r="E60" s="3">
-        <v>14835800</v>
+        <v>15213600</v>
       </c>
       <c r="F60" s="3">
-        <v>14861400</v>
+        <v>15239900</v>
       </c>
       <c r="G60" s="3">
-        <v>14842200</v>
+        <v>15220200</v>
       </c>
       <c r="H60" s="3">
-        <v>12627200</v>
+        <v>12948800</v>
       </c>
       <c r="I60" s="3">
-        <v>13671400</v>
+        <v>14019500</v>
       </c>
       <c r="J60" s="3">
-        <v>15136500</v>
+        <v>15522000</v>
       </c>
       <c r="K60" s="3">
         <v>15583000</v>
@@ -3802,25 +3802,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7638000</v>
+        <v>7832500</v>
       </c>
       <c r="E61" s="3">
-        <v>7792800</v>
+        <v>7991300</v>
       </c>
       <c r="F61" s="3">
-        <v>7113400</v>
+        <v>7294500</v>
       </c>
       <c r="G61" s="3">
-        <v>7266900</v>
+        <v>7452000</v>
       </c>
       <c r="H61" s="3">
-        <v>8703900</v>
+        <v>8925600</v>
       </c>
       <c r="I61" s="3">
-        <v>8299600</v>
+        <v>8510900</v>
       </c>
       <c r="J61" s="3">
-        <v>7751900</v>
+        <v>7949300</v>
       </c>
       <c r="K61" s="3">
         <v>7830400</v>
@@ -3867,25 +3867,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>987900</v>
+        <v>1013000</v>
       </c>
       <c r="E62" s="3">
-        <v>1614900</v>
+        <v>1656000</v>
       </c>
       <c r="F62" s="3">
-        <v>2216300</v>
+        <v>2272700</v>
       </c>
       <c r="G62" s="3">
-        <v>2414600</v>
+        <v>2476100</v>
       </c>
       <c r="H62" s="3">
-        <v>2327600</v>
+        <v>2386900</v>
       </c>
       <c r="I62" s="3">
-        <v>1719800</v>
+        <v>1763600</v>
       </c>
       <c r="J62" s="3">
-        <v>859900</v>
+        <v>881800</v>
       </c>
       <c r="K62" s="3">
         <v>1956000</v>
@@ -4127,25 +4127,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23279900</v>
+        <v>23872900</v>
       </c>
       <c r="E66" s="3">
-        <v>24243500</v>
+        <v>24860900</v>
       </c>
       <c r="F66" s="3">
-        <v>24191000</v>
+        <v>24807100</v>
       </c>
       <c r="G66" s="3">
-        <v>24523700</v>
+        <v>25148300</v>
       </c>
       <c r="H66" s="3">
-        <v>23658700</v>
+        <v>24261300</v>
       </c>
       <c r="I66" s="3">
-        <v>23690700</v>
+        <v>24294100</v>
       </c>
       <c r="J66" s="3">
-        <v>23748300</v>
+        <v>24353100</v>
       </c>
       <c r="K66" s="3">
         <v>25369400</v>
@@ -4477,25 +4477,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6090900</v>
+        <v>6246100</v>
       </c>
       <c r="E72" s="3">
-        <v>6550300</v>
+        <v>6717200</v>
       </c>
       <c r="F72" s="3">
-        <v>6606600</v>
+        <v>6774900</v>
       </c>
       <c r="G72" s="3">
-        <v>7487000</v>
+        <v>7677700</v>
       </c>
       <c r="H72" s="3">
-        <v>8124200</v>
+        <v>8331200</v>
       </c>
       <c r="I72" s="3">
-        <v>6523500</v>
+        <v>6689600</v>
       </c>
       <c r="J72" s="3">
-        <v>5941200</v>
+        <v>6092500</v>
       </c>
       <c r="K72" s="3">
         <v>6555300</v>
@@ -4737,25 +4737,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8788400</v>
+        <v>9012200</v>
       </c>
       <c r="E76" s="3">
-        <v>9242600</v>
+        <v>9478000</v>
       </c>
       <c r="F76" s="3">
-        <v>9281000</v>
+        <v>9517400</v>
       </c>
       <c r="G76" s="3">
-        <v>10146000</v>
+        <v>10404400</v>
       </c>
       <c r="H76" s="3">
-        <v>10778200</v>
+        <v>11052700</v>
       </c>
       <c r="I76" s="3">
-        <v>9164600</v>
+        <v>9398000</v>
       </c>
       <c r="J76" s="3">
-        <v>8574700</v>
+        <v>8793100</v>
       </c>
       <c r="K76" s="3">
         <v>9164100</v>
@@ -4937,25 +4937,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-23000</v>
+        <v>-23600</v>
       </c>
       <c r="E81" s="3">
-        <v>198300</v>
+        <v>203400</v>
       </c>
       <c r="F81" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="G81" s="3">
-        <v>364700</v>
+        <v>374000</v>
       </c>
       <c r="H81" s="3">
-        <v>368500</v>
+        <v>377900</v>
       </c>
       <c r="I81" s="3">
-        <v>483700</v>
+        <v>496000</v>
       </c>
       <c r="J81" s="3">
-        <v>-30700</v>
+        <v>-31500</v>
       </c>
       <c r="K81" s="3">
         <v>-233300</v>
@@ -5027,25 +5027,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>699900</v>
+        <v>717800</v>
       </c>
       <c r="E83" s="3">
-        <v>807400</v>
+        <v>828000</v>
       </c>
       <c r="F83" s="3">
-        <v>714000</v>
+        <v>732200</v>
       </c>
       <c r="G83" s="3">
-        <v>831700</v>
+        <v>852900</v>
       </c>
       <c r="H83" s="3">
-        <v>717900</v>
+        <v>736100</v>
       </c>
       <c r="I83" s="3">
-        <v>843300</v>
+        <v>864700</v>
       </c>
       <c r="J83" s="3">
-        <v>752400</v>
+        <v>771600</v>
       </c>
       <c r="K83" s="3">
         <v>842800</v>
@@ -5417,25 +5417,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>871400</v>
+        <v>893600</v>
       </c>
       <c r="E89" s="3">
-        <v>1643000</v>
+        <v>1684900</v>
       </c>
       <c r="F89" s="3">
-        <v>789500</v>
+        <v>809600</v>
       </c>
       <c r="G89" s="3">
-        <v>2006400</v>
+        <v>2057500</v>
       </c>
       <c r="H89" s="3">
-        <v>122800</v>
+        <v>126000</v>
       </c>
       <c r="I89" s="3">
-        <v>1168300</v>
+        <v>1198000</v>
       </c>
       <c r="J89" s="3">
-        <v>1064600</v>
+        <v>1091800</v>
       </c>
       <c r="K89" s="3">
         <v>1926700</v>
@@ -5702,25 +5702,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-508000</v>
+        <v>-520900</v>
       </c>
       <c r="E94" s="3">
-        <v>-790800</v>
+        <v>-810900</v>
       </c>
       <c r="F94" s="3">
-        <v>-556600</v>
+        <v>-570800</v>
       </c>
       <c r="G94" s="3">
-        <v>-369800</v>
+        <v>-379200</v>
       </c>
       <c r="H94" s="3">
-        <v>-470900</v>
+        <v>-482900</v>
       </c>
       <c r="I94" s="3">
-        <v>-359600</v>
+        <v>-368700</v>
       </c>
       <c r="J94" s="3">
-        <v>-371100</v>
+        <v>-380500</v>
       </c>
       <c r="K94" s="3">
         <v>-335400</v>
@@ -5792,10 +5792,10 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-116400</v>
+        <v>-119400</v>
       </c>
       <c r="E96" s="3">
-        <v>-275100</v>
+        <v>-282100</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -5807,10 +5807,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="J96" s="3">
-        <v>-29400</v>
+        <v>-30200</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6052,25 +6052,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-463200</v>
+        <v>-475000</v>
       </c>
       <c r="E100" s="3">
-        <v>102400</v>
+        <v>105000</v>
       </c>
       <c r="F100" s="3">
-        <v>-563000</v>
+        <v>-577400</v>
       </c>
       <c r="G100" s="3">
-        <v>-665400</v>
+        <v>-682300</v>
       </c>
       <c r="H100" s="3">
-        <v>-441500</v>
+        <v>-452700</v>
       </c>
       <c r="I100" s="3">
-        <v>-861200</v>
+        <v>-883100</v>
       </c>
       <c r="J100" s="3">
-        <v>-664100</v>
+        <v>-681000</v>
       </c>
       <c r="K100" s="3">
         <v>-1006100</v>
@@ -6182,25 +6182,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-99800</v>
+        <v>-102400</v>
       </c>
       <c r="E102" s="3">
-        <v>954600</v>
+        <v>978900</v>
       </c>
       <c r="F102" s="3">
-        <v>-330100</v>
+        <v>-338500</v>
       </c>
       <c r="G102" s="3">
-        <v>971200</v>
+        <v>996000</v>
       </c>
       <c r="H102" s="3">
-        <v>-789500</v>
+        <v>-809600</v>
       </c>
       <c r="I102" s="3">
-        <v>-52500</v>
+        <v>-53800</v>
       </c>
       <c r="J102" s="3">
-        <v>29400</v>
+        <v>30200</v>
       </c>
       <c r="K102" s="3">
         <v>585300</v>

--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>JSAIY</t>
   </si>
@@ -656,306 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45549</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45549</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45457</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45457</v>
+      </c>
+      <c r="H7" s="2">
         <v>45353</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
+        <v>45262</v>
+      </c>
+      <c r="J7" s="2">
         <v>45185</v>
       </c>
-      <c r="F7" s="2">
-        <v>44989</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44821</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>44625</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>44457</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>44261</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>44093</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>43897</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>43729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>43533</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>43365</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>43169</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>43001</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>42805</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>42637</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>42441</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>42273</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>42077</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>20623800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>22285100</v>
-      </c>
-      <c r="F8" s="3">
-        <v>19791900</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>21530600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>18595200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>20633000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>18520400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>19042300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>17610400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>18732400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>16418700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>18453400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>18836700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>20722900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>17939000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>16343700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>14460900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>16198200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>14626900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>16679800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>19046600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>20546400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>18125400</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>19923100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>17140000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>18995400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>17355200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>17397500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>16130200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>17335200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>15099700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>17022500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>17614700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>19327600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>16791200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>15354700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>13549200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>15210900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>13693300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>16022700</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>1577300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1738700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1666500</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>1607400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>1455200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>1637600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>1165200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>1644900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>1480200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>1397100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>1318900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>1430900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>1222000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>1395300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>1147800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>989000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>911700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>987400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>933600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>657100</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -979,8 +1026,12 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,8 +1095,20 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,96 +1172,120 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>447500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>148300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>618000</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-7900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="L14" s="3">
         <v>28900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>-147000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="N14" s="3">
         <v>112800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>555900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="P14" s="3">
         <v>140700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="Q14" s="3">
         <v>277900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="R14" s="3">
         <v>30800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="S14" s="3">
         <v>-17100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1239,8 +1326,20 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1261,138 +1360,166 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>20442800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>21716900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>19690900</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>20832500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>17969300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>19753900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>18368200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>18967100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>17069300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>18419700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>16096900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>18063100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>18516200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>20322400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>17694600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>15752900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>14090500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>15646500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>14212100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>16987900</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>181100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>568200</v>
-      </c>
-      <c r="F18" s="3">
-        <v>101000</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>698100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>625900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>879200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>152200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>75200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>541100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>312700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>321700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>390400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>320500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>400500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>244300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>590800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>370400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>551700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>414800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1416,333 +1543,397 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>23600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>15700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>17100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
         <v>-31500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
         <v>36700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="N20" s="3">
         <v>10500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>-6400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>-10100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>-43400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <v>10600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <v>11000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="T20" s="3">
         <v>8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>-8500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>-2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
         <v>-29700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>-24800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>-26100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>-48700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>922500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1411900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>850300</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>1557600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>1330600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>1780700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>934300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>911700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>1277400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>1096900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>1019700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>1232100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>831900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>904300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>639300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>983800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>705600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>927400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>709700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>119800</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>202100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>223100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>182400</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>211300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="L22" s="3">
         <v>183700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="M22" s="3">
         <v>224400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="N22" s="3">
         <v>196800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="O22" s="3">
         <v>243500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="P22" s="3">
         <v>219200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3">
         <v>258100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="R22" s="3">
         <v>220000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="S22" s="3">
         <v>270800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="T22" s="3">
         <v>70900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="U22" s="3">
         <v>80700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <v>68700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>80200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>73000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>83500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>79000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>2600</v>
-      </c>
-      <c r="E23" s="3">
-        <v>360900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-64300</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>493400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>410700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>691500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>-34100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>-174700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>311800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>11200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>112400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>130500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>257800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>311300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>173000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>480900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>272600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>442200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>287100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>-381900</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>26200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>157500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>38100</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>119400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="L24" s="3">
         <v>32800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
         <v>195500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>-6600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>53600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>71000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>58300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="R24" s="3">
         <v>37900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="S24" s="3">
         <v>-19500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="T24" s="3">
         <v>62700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>76400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>70000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>94400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>97800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>52700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>71100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1806,138 +1997,174 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E26" s="3">
-        <v>203400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-102400</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>374000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>377900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>496000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>-27600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>-228200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>240800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>-47200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>74500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>150000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>195000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>234900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>103000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>386600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>270000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>344300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>234400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>203400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-102400</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>374000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>377900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>496000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>-31500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>-233300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>225600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>-60800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>65100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>137800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>184100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>220800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>92500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>373600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>256900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>341700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>234400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2001,31 +2228,43 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2066,8 +2305,20 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2131,8 +2382,20 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2196,138 +2459,174 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-17100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
         <v>31500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
         <v>-36700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="N32" s="3">
         <v>-10500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>6400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>10100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>43400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="R32" s="3">
         <v>-10600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
         <v>-11000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="T32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="U32" s="3">
         <v>8500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="V32" s="3">
         <v>2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="W32" s="3">
         <v>29700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="X32" s="3">
         <v>24800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="Y32" s="3">
         <v>26100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Z32" s="3">
         <v>48700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="AA32" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>203400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-102400</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>374000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>377900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>496000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>-31500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-233300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>225600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>-60800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>65100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>137800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>184100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>220800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>92500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>373600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>256900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>341700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>234400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2391,143 +2690,179 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>203400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-102400</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>374000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>377900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>496000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>-31500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-233300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>225600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>-60800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>65100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>137800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>184100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>220800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>92500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>373600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>256900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>341700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>234400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45549</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45549</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45457</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45457</v>
+      </c>
+      <c r="H38" s="2">
         <v>45353</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
+        <v>45262</v>
+      </c>
+      <c r="J38" s="2">
         <v>45185</v>
       </c>
-      <c r="F38" s="2">
-        <v>44989</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44821</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>44625</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>44457</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>44261</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>44093</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>43897</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>43729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>43533</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>43365</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>43169</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>43001</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>42805</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>42637</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>42441</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>42273</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>42077</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2551,8 +2886,12 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2576,593 +2915,705 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1444700</v>
+        <v>1194800</v>
       </c>
       <c r="E41" s="3">
-        <v>1495900</v>
+        <v>1194800</v>
       </c>
       <c r="F41" s="3">
-        <v>1278100</v>
+        <v>1152800</v>
       </c>
       <c r="G41" s="3">
+        <v>1152800</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2510600</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2518500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1076500</v>
+      </c>
+      <c r="K41" s="3">
         <v>1558900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>775500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>1426400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>948700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>2111600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>2173400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>1372300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>961700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>1095500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>1427900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>1542500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>1112100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>1383300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>1113900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>1494700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>1692100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>1865900</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1184900</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>1263600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>1100900</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1199400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>564200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>867400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>1236100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>603100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>449900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>675000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="R42" s="3">
         <v>613900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="S42" s="3">
         <v>1119900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="T42" s="3">
         <v>1208300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="U42" s="3">
         <v>536300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="V42" s="3">
         <v>450400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="W42" s="3">
         <v>309000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="X42" s="3">
         <v>439600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="Y42" s="3">
         <v>156500</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4765900</v>
+        <v>897700</v>
       </c>
       <c r="E43" s="3">
-        <v>5225200</v>
+        <v>897700</v>
       </c>
       <c r="F43" s="3">
-        <v>5394500</v>
+        <v>866200</v>
       </c>
       <c r="G43" s="3">
+        <v>866200</v>
+      </c>
+      <c r="H43" s="3">
+        <v>495300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>496900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>829700</v>
+      </c>
+      <c r="K43" s="3">
         <v>5252700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>5046700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>8773400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>9157800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>9573500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>11042000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>5584800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>5048600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>5044300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>5597000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>5115600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>4305800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>4140900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>2873400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>2986900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>2725800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>2561200</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2528600</v>
+        <v>2531500</v>
       </c>
       <c r="E44" s="3">
-        <v>2869800</v>
+        <v>2531500</v>
       </c>
       <c r="F44" s="3">
-        <v>2491900</v>
+        <v>2442500</v>
       </c>
       <c r="G44" s="3">
+        <v>2442500</v>
+      </c>
+      <c r="H44" s="3">
+        <v>2434800</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2442500</v>
+      </c>
+      <c r="J44" s="3">
+        <v>2712400</v>
+      </c>
+      <c r="K44" s="3">
         <v>2481400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>2358000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>2207100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>2132300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>2084800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>2195000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>2423300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>2281800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>2292200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>2468500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>2728300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>2344400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>2460200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>1262600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>1321300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>1312800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>1389200</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10500</v>
+        <v>4112700</v>
       </c>
       <c r="E45" s="3">
-        <v>140400</v>
+        <v>4112700</v>
       </c>
       <c r="F45" s="3">
-        <v>91900</v>
+        <v>3968100</v>
       </c>
       <c r="G45" s="3">
+        <v>3968100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>22800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>145100</v>
+      </c>
+      <c r="K45" s="3">
         <v>147000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>102400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>26200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>35700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>50900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>24800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>57300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>13600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>25500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>124200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>175800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>66500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>58700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>90900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>9934700</v>
+        <v>11068500</v>
       </c>
       <c r="E46" s="3">
-        <v>10994900</v>
+        <v>11068500</v>
       </c>
       <c r="F46" s="3">
-        <v>10357200</v>
+        <v>10679400</v>
       </c>
       <c r="G46" s="3">
+        <v>10679400</v>
+      </c>
+      <c r="H46" s="3">
+        <v>9578900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>9609000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>10404200</v>
+      </c>
+      <c r="K46" s="3">
         <v>10639300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>8846900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>9399300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>9378300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>10098800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>9608700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>10106300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>8930900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>9609200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>10715300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>9948200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>8336800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>8469200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>5755900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>6018100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>5821500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>5878200</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3067900</v>
+        <v>18400</v>
       </c>
       <c r="E47" s="3">
-        <v>2951100</v>
+        <v>18400</v>
       </c>
       <c r="F47" s="3">
-        <v>3255600</v>
+        <v>17800</v>
       </c>
       <c r="G47" s="3">
+        <v>17800</v>
+      </c>
+      <c r="H47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>24100</v>
+      </c>
+      <c r="J47" s="3">
+        <v>828500</v>
+      </c>
+      <c r="K47" s="3">
         <v>3070500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>3540300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>3586200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>7045200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>8344300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>10049700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>5629500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>5034400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>4342800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>4293200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>4044400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>3509300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>3243700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>3155100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>2870800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>2683600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>2766600</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17817100</v>
+        <v>17832300</v>
       </c>
       <c r="E48" s="3">
-        <v>17643800</v>
+        <v>17832300</v>
       </c>
       <c r="F48" s="3">
-        <v>17775100</v>
+        <v>17205400</v>
       </c>
       <c r="G48" s="3">
+        <v>17205400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>17156300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>17210200</v>
+      </c>
+      <c r="J48" s="3">
+        <v>16676000</v>
+      </c>
+      <c r="K48" s="3">
         <v>18013900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>18320900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>17897100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>28764700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>28404100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>28750000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>17149100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>16780600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>17492100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>13498800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>14078900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>13215800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>12974600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>12735300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>12722200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>12704400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>12620100</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1057600</v>
+        <v>1066000</v>
       </c>
       <c r="E49" s="3">
-        <v>1324000</v>
+        <v>1066000</v>
       </c>
       <c r="F49" s="3">
-        <v>1343700</v>
+        <v>1028500</v>
       </c>
       <c r="G49" s="3">
+        <v>1028500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1018400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1021600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1251400</v>
+      </c>
+      <c r="K49" s="3">
         <v>1339800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>1320100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>1313500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>1199400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>1094000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>1234400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>1250700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>1233800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>1282100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>1462000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>1178800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>1060600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>1027800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="X49" s="3">
         <v>429100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
         <v>448700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>428000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>399000</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3226,8 +3677,20 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3291,73 +3754,97 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1007800</v>
+        <v>1008100</v>
       </c>
       <c r="E52" s="3">
-        <v>1425000</v>
+        <v>1008100</v>
       </c>
       <c r="F52" s="3">
-        <v>1593000</v>
+        <v>972700</v>
       </c>
       <c r="G52" s="3">
+        <v>972700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1094200</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1097700</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1334500</v>
+      </c>
+      <c r="K52" s="3">
         <v>2489200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>3285700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>1495900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>1018300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>1298100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>1430800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>1730900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>1154500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>356200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>35500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>12700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>26400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>60800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>62600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>71700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>138300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3421,73 +3908,97 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>32885000</v>
+        <v>32381300</v>
       </c>
       <c r="E54" s="3">
-        <v>34339000</v>
+        <v>32381300</v>
       </c>
       <c r="F54" s="3">
-        <v>34324500</v>
+        <v>31242900</v>
       </c>
       <c r="G54" s="3">
+        <v>31242900</v>
+      </c>
+      <c r="H54" s="3">
+        <v>31665500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>31765000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>32455300</v>
+      </c>
+      <c r="K54" s="3">
         <v>35552700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>35313900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>33692000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>33146200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>34533500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>35404600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>35866600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>33134200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>33082500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>30004700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>29263100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>26149000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>25776000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>22138100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>22131500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>21775800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>21715200</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3511,8 +4022,12 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3536,398 +4051,474 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6680400</v>
+        <v>6694200</v>
       </c>
       <c r="E57" s="3">
-        <v>6925800</v>
+        <v>6694200</v>
       </c>
       <c r="F57" s="3">
-        <v>6347100</v>
+        <v>6458900</v>
       </c>
       <c r="G57" s="3">
+        <v>6458900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>4755900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>4770900</v>
+      </c>
+      <c r="J57" s="3">
+        <v>6545900</v>
+      </c>
+      <c r="K57" s="3">
         <v>6516400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>5965300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>5987600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>5889200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>5995500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>5417700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>5844200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>5172800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>5833600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>5894300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>5920800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>4941100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>5511200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>8151900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>8526300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>8369500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>8190400</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>782100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>782100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>754600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>754600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>732900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>735200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>703200</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2083800</v>
+      </c>
+      <c r="L58" s="3">
         <v>761100</v>
       </c>
-      <c r="E58" s="3">
-        <v>704700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2081100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2083800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>761100</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>1074700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>1154700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>1797900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>707200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>1279300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>1595700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>933200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="T58" s="3">
         <v>870100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="U58" s="3">
         <v>984900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="V58" s="3">
         <v>454400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>586900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>290900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>230900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>342400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>492500</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7585800</v>
+        <v>5273300</v>
       </c>
       <c r="E59" s="3">
-        <v>7583200</v>
+        <v>5273300</v>
       </c>
       <c r="F59" s="3">
-        <v>6811600</v>
+        <v>5087900</v>
       </c>
       <c r="G59" s="3">
+        <v>5087900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1392400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1396800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>388200</v>
+      </c>
+      <c r="K59" s="3">
         <v>6620000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>6222500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>6957300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>8478100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>7789600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>9146100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>8557800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>7247600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>6802200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>7285400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>7275100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>6172100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>5257900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>322200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>277800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>404300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>358200</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>15027300</v>
+        <v>14877600</v>
       </c>
       <c r="E60" s="3">
-        <v>15213600</v>
+        <v>14877600</v>
       </c>
       <c r="F60" s="3">
-        <v>15239900</v>
+        <v>14354600</v>
       </c>
       <c r="G60" s="3">
+        <v>14354600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>14470000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>14515500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>14379100</v>
+      </c>
+      <c r="K60" s="3">
         <v>15220200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>12948800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>14019500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>15522000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>15583000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>15271000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>15681200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>14016200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>13568900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>14049800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>14180800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>11340300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>11062600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>8765000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>9035000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>9116100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>9041100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7832500</v>
+        <v>7908700</v>
       </c>
       <c r="E61" s="3">
-        <v>7991300</v>
+        <v>7908700</v>
       </c>
       <c r="F61" s="3">
-        <v>7294500</v>
+        <v>7630700</v>
       </c>
       <c r="G61" s="3">
+        <v>7630700</v>
+      </c>
+      <c r="H61" s="3">
+        <v>7542000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>7565800</v>
+      </c>
+      <c r="J61" s="3">
+        <v>7639700</v>
+      </c>
+      <c r="K61" s="3">
         <v>7452000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>8925600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>8510900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>7949300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>7830400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>8252700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>7771100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>7265400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>8113600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="T61" s="3">
         <v>2184800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="U61" s="3">
         <v>2042000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="V61" s="3">
         <v>2693100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="W61" s="3">
         <v>2731700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="X61" s="3">
         <v>2856400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="Y61" s="3">
         <v>3018200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Z61" s="3">
         <v>3299900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>3443400</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1013000</v>
+        <v>395600</v>
       </c>
       <c r="E62" s="3">
-        <v>1656000</v>
+        <v>395600</v>
       </c>
       <c r="F62" s="3">
-        <v>2272700</v>
+        <v>381700</v>
       </c>
       <c r="G62" s="3">
+        <v>381700</v>
+      </c>
+      <c r="H62" s="3">
+        <v>298200</v>
+      </c>
+      <c r="I62" s="3">
+        <v>299100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>182300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2476100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>2386900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>1763600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>881800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>1956000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>2007400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>2604400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>2647300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>2648400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>3663100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>3223600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>3039100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>3586300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>2214700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>1977300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>2066000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>1966000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3991,8 +4582,20 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4056,8 +4659,20 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4121,73 +4736,97 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>23872900</v>
+        <v>23689200</v>
       </c>
       <c r="E66" s="3">
-        <v>24860900</v>
+        <v>23689200</v>
       </c>
       <c r="F66" s="3">
-        <v>24807100</v>
+        <v>22856500</v>
       </c>
       <c r="G66" s="3">
+        <v>22856500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>22987500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>23059800</v>
+      </c>
+      <c r="J66" s="3">
+        <v>23497200</v>
+      </c>
+      <c r="K66" s="3">
         <v>25148300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>24261300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>24294100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>24353100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>25369400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>25531000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>26056800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>23928900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>24330900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>19897700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>19446400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>17072500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>17380500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>13836100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>14030500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>14482100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>14450500</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4211,8 +4850,12 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4276,8 +4919,20 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4341,8 +4996,20 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4406,8 +5073,20 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4471,73 +5150,97 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6246100</v>
+        <v>5268100</v>
       </c>
       <c r="E72" s="3">
-        <v>6717200</v>
+        <v>5268100</v>
       </c>
       <c r="F72" s="3">
-        <v>6774900</v>
+        <v>5082900</v>
       </c>
       <c r="G72" s="3">
+        <v>5082900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>4090100</v>
+      </c>
+      <c r="I72" s="3">
+        <v>4102900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4407700</v>
+      </c>
+      <c r="K72" s="3">
         <v>7677700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>8331200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>6689600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>6092500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>6555300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>6972700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>6982000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>6516600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>5988500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>7034400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>6639700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>6116600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>5500900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>5484600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>5285100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>5113100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>5098600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4601,8 +5304,20 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4666,8 +5381,20 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4731,73 +5458,97 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9012200</v>
+        <v>8692100</v>
       </c>
       <c r="E76" s="3">
-        <v>9478000</v>
+        <v>8692100</v>
       </c>
       <c r="F76" s="3">
-        <v>9517400</v>
+        <v>8386500</v>
       </c>
       <c r="G76" s="3">
+        <v>8386500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>8678000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>8705200</v>
+      </c>
+      <c r="J76" s="3">
+        <v>8958100</v>
+      </c>
+      <c r="K76" s="3">
         <v>10404400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>11052700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>9398000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>8793100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>9164100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>9873500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>9809800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>9205300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>8751600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>10107000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>9816600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>9076500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>8395500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>8301900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>8101100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>7293700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>7264700</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4861,143 +5612,179 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45549</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45549</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45457</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45457</v>
+      </c>
+      <c r="H80" s="2">
         <v>45353</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
+        <v>45262</v>
+      </c>
+      <c r="J80" s="2">
         <v>45185</v>
       </c>
-      <c r="F80" s="2">
-        <v>44989</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44821</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>44625</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>44457</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>44261</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>44093</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>43897</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>43729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>43533</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>43365</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>43169</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>43001</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>42805</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>42637</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>42441</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>42273</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>42077</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>203400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-102400</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>374000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>377900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>496000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>-31500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-233300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>225600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>-60800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>65100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>137800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>184100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>220800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>92500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>373600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>256900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>341700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>234400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5021,73 +5808,89 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>717800</v>
+        <v>230600</v>
       </c>
       <c r="E83" s="3">
-        <v>828000</v>
+        <v>231300</v>
       </c>
       <c r="F83" s="3">
-        <v>732200</v>
+        <v>323700</v>
       </c>
       <c r="G83" s="3">
+        <v>334600</v>
+      </c>
+      <c r="H83" s="3">
+        <v>239600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>245000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>315200</v>
+      </c>
+      <c r="K83" s="3">
         <v>852900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>736100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>864700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>771600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>842800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>746400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>827600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>687300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>830800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="T83" s="3">
         <v>503200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="U83" s="3">
         <v>512300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>397600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>422700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>360000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>401700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>343700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5151,8 +5954,20 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5216,8 +6031,20 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5281,8 +6108,20 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5346,8 +6185,20 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5411,73 +6262,97 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>893600</v>
+        <v>418000</v>
       </c>
       <c r="E89" s="3">
-        <v>1684900</v>
+        <v>418000</v>
       </c>
       <c r="F89" s="3">
-        <v>809600</v>
+        <v>403300</v>
       </c>
       <c r="G89" s="3">
+        <v>403300</v>
+      </c>
+      <c r="H89" s="3">
+        <v>430200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>431600</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1065300</v>
+      </c>
+      <c r="K89" s="3">
         <v>2057500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>126000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>1198000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>1091800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>1926700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>441000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>1270600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>105300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>1163800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>782800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>1119400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>537600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>964400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>189100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>322200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>675500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>524100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5501,73 +6376,89 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-429000</v>
+        <v>-194500</v>
       </c>
       <c r="E91" s="3">
-        <v>-1130000</v>
+        <v>-194500</v>
       </c>
       <c r="F91" s="3">
-        <v>-430000</v>
+        <v>-187700</v>
       </c>
       <c r="G91" s="3">
+        <v>-187700</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-214800</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-215500</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-645500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-308000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-375000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-319000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-294000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-301000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-374000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-265000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-282700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-286700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
         <v>-380500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="U91" s="3">
         <v>-399100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="V91" s="3">
         <v>-431900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="W91" s="3">
         <v>-396900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="X91" s="3">
         <v>-373000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-469600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>-583300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="AA91" s="3">
         <v>-771600</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5631,8 +6522,20 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5696,73 +6599,97 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-520900</v>
+        <v>-266800</v>
       </c>
       <c r="E94" s="3">
-        <v>-810900</v>
+        <v>-266800</v>
       </c>
       <c r="F94" s="3">
-        <v>-570800</v>
+        <v>-257400</v>
       </c>
       <c r="G94" s="3">
+        <v>-257400</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-250800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-251600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-652400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-379200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-482900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-368700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-380500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-335400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-422000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-115400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-308700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-259800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>-261800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-393400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <v>-394900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-583100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-113500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-408200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-454300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-730800</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5786,73 +6713,89 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-119400</v>
+        <v>142600</v>
       </c>
       <c r="E96" s="3">
-        <v>-282100</v>
+        <v>142600</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>137600</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>137600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>57500</v>
       </c>
       <c r="I96" s="3">
+        <v>57700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>133300</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-5200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>-30200</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="Q96" s="3">
         <v>-24800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="R96" s="3">
         <v>-3500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>-24400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="T96" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="U96" s="3">
         <v>-28300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="V96" s="3">
         <v>-4000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="W96" s="3">
         <v>-25900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="X96" s="3">
         <v>199600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="Y96" s="3">
         <v>-204800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="Z96" s="3">
         <v>-126400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="AA96" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5916,8 +6859,20 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5981,8 +6936,20 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6046,96 +7013,120 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-475000</v>
+        <v>-414000</v>
       </c>
       <c r="E100" s="3">
-        <v>105000</v>
+        <v>-414000</v>
       </c>
       <c r="F100" s="3">
-        <v>-577400</v>
+        <v>-399500</v>
       </c>
       <c r="G100" s="3">
+        <v>-399500</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-228700</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-229400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>49600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-682300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-452700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-883100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-681000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-1006100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-618400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-724600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-912500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>19100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="U100" s="3">
         <v>-365100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="V100" s="3">
         <v>-281300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="W100" s="3">
         <v>-327100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="X100" s="3">
         <v>-233500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>66500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-385800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6176,69 +7167,93 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-102400</v>
+        <v>-262900</v>
       </c>
       <c r="E102" s="3">
-        <v>978900</v>
+        <v>-262900</v>
       </c>
       <c r="F102" s="3">
-        <v>-338500</v>
+        <v>-253600</v>
       </c>
       <c r="G102" s="3">
+        <v>-253600</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>462600</v>
+      </c>
+      <c r="K102" s="3">
         <v>996000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-809600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>-53800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>30200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>585300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-599400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>430600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-404600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-324500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>540100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>360900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>-138700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>54300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>-157800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>-19600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>-164600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>-234400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>JSAIY</t>
   </si>
@@ -656,24 +656,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -681,31 +682,33 @@
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45717</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45627</v>
+      </c>
+      <c r="F7" s="2">
         <v>45549</v>
-      </c>
-      <c r="E7" s="2">
-        <v>45549</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45457</v>
       </c>
       <c r="G7" s="2">
         <v>45457</v>
@@ -720,58 +723,64 @@
         <v>45185</v>
       </c>
       <c r="K7" s="2">
+        <v>45262</v>
+      </c>
+      <c r="L7" s="2">
+        <v>45185</v>
+      </c>
+      <c r="M7" s="2">
         <v>44821</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44625</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44457</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44261</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44093</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43897</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43729</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43533</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43365</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43169</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43001</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42805</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42637</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42441</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42273</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42077</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -796,59 +805,65 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>21530600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>18595200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>20633000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18520400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>19042300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>17610400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18732400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>16418700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>18453400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>18836700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20722900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>17939000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>16343700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>14460900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>16198200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>14626900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>16679800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -873,59 +888,65 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>19923100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>17140000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>18995400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>17355200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>17397500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>16130200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>17335200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>15099700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>17022500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>17614700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>19327600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>16791200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>15354700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>13549200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>15210900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>13693300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>16022700</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -950,59 +971,65 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>1607400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1455200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1637600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1165200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1644900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1480200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1397100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1318900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1430900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1222000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1395300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1147800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>989000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>911700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>987400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>933600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>657100</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1057,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1136,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1219,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1210,50 +1251,50 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-7900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>28900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-147000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>112800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>555900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>140700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>277900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>30800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-17100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1261,8 +1302,14 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1287,11 +1334,11 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1338,8 +1385,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,8 +1417,10 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1390,59 +1445,65 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>20832500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>17969300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>19753900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>18368200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>18967100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>17069300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>18419700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16096900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>18063100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>18516200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>20322400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>17694600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>15752900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>14090500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>15646500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>14212100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>16987900</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1467,59 +1528,65 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>698100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>625900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>879200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>152200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>75200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>541100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>312700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>321700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>390400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>320500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>400500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>244300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>590800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>370400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>551700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>414800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1614,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1573,59 +1642,65 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-31500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>36700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>10500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-6400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-43400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>10600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>11000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-8500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-29700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1650,59 +1725,65 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>1557600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1330600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1780700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>934300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>911700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1277400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1096900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1019700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1232100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>831900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>904300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>639300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>983800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>705600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>927400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>709700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>119800</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1727,59 +1808,65 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>211300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>183700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>224400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>196800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>243500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>219200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>258100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>220000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>270800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>70900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>80700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>68700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>80200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>73000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>83500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>79000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1804,59 +1891,65 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>493400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>410700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>691500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-34100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-174700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>311800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>11200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>112400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>130500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>257800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>311300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>173000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>480900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>272600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>442200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>287100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-381900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1881,59 +1974,65 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>119400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>32800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>195500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-6600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>53600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>71000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>58300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>37900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-19500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>62700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>76400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>70000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>94400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>97800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>52700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>71100</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,8 +2108,14 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2035,59 +2140,65 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>374000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>377900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>496000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-27600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-228200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>240800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-47200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>74500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>150000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>195000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>234900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>103000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>386600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>270000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>344300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>234400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2112,59 +2223,65 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>374000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>377900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>496000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-31500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-233300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>225600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-60800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>65100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>137800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>184100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>220800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>92500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>373600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>256900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>341700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>234400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2357,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2266,11 +2389,11 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2317,8 +2440,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2523,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2606,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2497,59 +2638,65 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>31500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-36700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-10500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>6400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>10100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>43400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-10600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-11000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>8500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>29700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>24800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>26100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>48700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2574,59 +2721,65 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>374000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>377900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>496000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-31500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-233300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>225600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-60800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>65100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>137800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>184100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>220800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>92500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>373600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>256900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>341700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>234400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,8 +2855,14 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2728,75 +2887,81 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>374000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>377900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>496000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-31500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-233300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>225600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-60800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>65100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>137800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>184100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>220800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>92500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>373600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>256900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>341700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>234400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45717</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45627</v>
+      </c>
+      <c r="F38" s="2">
         <v>45549</v>
-      </c>
-      <c r="E38" s="2">
-        <v>45549</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45457</v>
       </c>
       <c r="G38" s="2">
         <v>45457</v>
@@ -2811,58 +2976,64 @@
         <v>45185</v>
       </c>
       <c r="K38" s="2">
+        <v>45262</v>
+      </c>
+      <c r="L38" s="2">
+        <v>45185</v>
+      </c>
+      <c r="M38" s="2">
         <v>44821</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44625</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44457</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44261</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44093</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43897</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43729</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43533</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43365</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43169</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43001</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42805</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42637</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42441</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42273</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42077</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3061,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3092,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>914900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>923600</v>
+      </c>
+      <c r="F41" s="3">
         <v>1194800</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1194800</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1152800</v>
       </c>
       <c r="G41" s="3">
         <v>1152800</v>
       </c>
       <c r="H41" s="3">
-        <v>2510600</v>
+        <v>1108100</v>
       </c>
       <c r="I41" s="3">
-        <v>2518500</v>
+        <v>1111600</v>
       </c>
       <c r="J41" s="3">
         <v>1076500</v>
       </c>
       <c r="K41" s="3">
+        <v>2518500</v>
+      </c>
+      <c r="L41" s="3">
+        <v>1076500</v>
+      </c>
+      <c r="M41" s="3">
         <v>1558900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>775500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1426400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>948700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2111600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2173400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1372300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>961700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1095500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1427900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1542500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1112100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1383300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1113900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1494700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1692100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1865900</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3023,146 +3204,158 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1199400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>564200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>867400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1236100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>603100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>449900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>675000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>613900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>1119900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1208300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>536300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>450400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>309000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>439600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>156500</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>719800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>726700</v>
+      </c>
+      <c r="F43" s="3">
         <v>897700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>897700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>866200</v>
       </c>
       <c r="G43" s="3">
         <v>866200</v>
       </c>
       <c r="H43" s="3">
-        <v>495300</v>
+        <v>735400</v>
       </c>
       <c r="I43" s="3">
-        <v>496900</v>
+        <v>737700</v>
       </c>
       <c r="J43" s="3">
         <v>829700</v>
       </c>
       <c r="K43" s="3">
+        <v>496900</v>
+      </c>
+      <c r="L43" s="3">
+        <v>829700</v>
+      </c>
+      <c r="M43" s="3">
         <v>5252700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>5046700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8773400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>9157800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>9573500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>11042000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5584800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5048600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5044300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>5597000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5115600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>4305800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>4140900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>2873400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2986900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>2725800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>2561200</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2448900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2472300</v>
+      </c>
+      <c r="F44" s="3">
         <v>2531500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>2531500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>2442500</v>
       </c>
       <c r="G44" s="3">
         <v>2442500</v>
@@ -3177,146 +3370,158 @@
         <v>2712400</v>
       </c>
       <c r="K44" s="3">
+        <v>2442500</v>
+      </c>
+      <c r="L44" s="3">
+        <v>2712400</v>
+      </c>
+      <c r="M44" s="3">
         <v>2481400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2358000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2207100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2132300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2084800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2195000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2423300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2281800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2292200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2468500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2728300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2344400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2460200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1262600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1321300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1312800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1389200</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3969100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4007100</v>
+      </c>
+      <c r="F45" s="3">
         <v>4112700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4112700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3968100</v>
       </c>
       <c r="G45" s="3">
         <v>3968100</v>
       </c>
       <c r="H45" s="3">
-        <v>22700</v>
+        <v>44200</v>
       </c>
       <c r="I45" s="3">
-        <v>22800</v>
+        <v>44400</v>
       </c>
       <c r="J45" s="3">
         <v>145100</v>
       </c>
       <c r="K45" s="3">
+        <v>22800</v>
+      </c>
+      <c r="L45" s="3">
+        <v>145100</v>
+      </c>
+      <c r="M45" s="3">
         <v>147000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>102400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>26200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>35700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>15200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>50900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>24800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>57300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>13600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>25500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>124200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>175800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>66500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>58700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>90900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10632500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10734200</v>
+      </c>
+      <c r="F46" s="3">
         <v>11068500</v>
-      </c>
-      <c r="E46" s="3">
-        <v>11068500</v>
-      </c>
-      <c r="F46" s="3">
-        <v>10679400</v>
       </c>
       <c r="G46" s="3">
         <v>10679400</v>
@@ -3331,146 +3536,158 @@
         <v>10404200</v>
       </c>
       <c r="K46" s="3">
+        <v>9609000</v>
+      </c>
+      <c r="L46" s="3">
+        <v>10404200</v>
+      </c>
+      <c r="M46" s="3">
         <v>10639300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>8846900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9399300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>9378300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10098800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9608700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>10106300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>8930900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>9609200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10715300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>9948200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>8336800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8469200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>5755900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>6018100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5821500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5878200</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F47" s="3">
         <v>18400</v>
-      </c>
-      <c r="E47" s="3">
-        <v>18400</v>
-      </c>
-      <c r="F47" s="3">
-        <v>17800</v>
       </c>
       <c r="G47" s="3">
         <v>17800</v>
       </c>
       <c r="H47" s="3">
-        <v>24000</v>
+        <v>2500</v>
       </c>
       <c r="I47" s="3">
-        <v>24100</v>
+        <v>2500</v>
       </c>
       <c r="J47" s="3">
         <v>828500</v>
       </c>
       <c r="K47" s="3">
+        <v>24100</v>
+      </c>
+      <c r="L47" s="3">
+        <v>828500</v>
+      </c>
+      <c r="M47" s="3">
         <v>3070500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>3540300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3586200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>7045200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>8344300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>10049700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>5629500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5034400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4342800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>4293200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4044400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>3509300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3243700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>3155100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>2870800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>2683600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>2766600</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17382700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17549000</v>
+      </c>
+      <c r="F48" s="3">
         <v>17832300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>17832300</v>
-      </c>
-      <c r="F48" s="3">
-        <v>17205400</v>
       </c>
       <c r="G48" s="3">
         <v>17205400</v>
@@ -3485,69 +3702,75 @@
         <v>16676000</v>
       </c>
       <c r="K48" s="3">
+        <v>17210200</v>
+      </c>
+      <c r="L48" s="3">
+        <v>16676000</v>
+      </c>
+      <c r="M48" s="3">
         <v>18013900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>18320900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>17897100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>28764700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>28404100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>28750000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>17149100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>16780600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>17492100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13498800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>14078900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>13215800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>12974600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>12735300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>12722200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>12704400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12620100</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1015600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1025300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1066000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1066000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1028500</v>
       </c>
       <c r="G49" s="3">
         <v>1028500</v>
@@ -3562,58 +3785,64 @@
         <v>1251400</v>
       </c>
       <c r="K49" s="3">
+        <v>1021600</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1251400</v>
+      </c>
+      <c r="M49" s="3">
         <v>1339800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1320100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1313500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1199400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1094000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1234400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1250700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1233800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1282100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1462000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1178800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1060600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1027800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>429100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>448700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>428000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>399000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3918,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +4001,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1931700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1950200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1008100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1008100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>972700</v>
       </c>
       <c r="G52" s="3">
         <v>972700</v>
       </c>
       <c r="H52" s="3">
-        <v>1094200</v>
+        <v>1919300</v>
       </c>
       <c r="I52" s="3">
-        <v>1097700</v>
+        <v>1925300</v>
       </c>
       <c r="J52" s="3">
         <v>1334500</v>
       </c>
       <c r="K52" s="3">
+        <v>1097700</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1334500</v>
+      </c>
+      <c r="M52" s="3">
         <v>2489200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3285700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1495900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1018300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1298100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1430800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1730900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1154500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>356200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>35500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>12700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>26400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>60800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>62600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>71700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>138300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,19 +4167,25 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31017800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31314600</v>
+      </c>
+      <c r="F54" s="3">
         <v>32381300</v>
-      </c>
-      <c r="E54" s="3">
-        <v>32381300</v>
-      </c>
-      <c r="F54" s="3">
-        <v>31242900</v>
       </c>
       <c r="G54" s="3">
         <v>31242900</v>
@@ -3947,58 +4200,64 @@
         <v>32455300</v>
       </c>
       <c r="K54" s="3">
+        <v>31765000</v>
+      </c>
+      <c r="L54" s="3">
+        <v>32455300</v>
+      </c>
+      <c r="M54" s="3">
         <v>35552700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>35313900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>33692000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>33146200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>34533500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35404600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>35866600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>33134200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>33082500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>30004700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>29263100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>26149000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>25776000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>22138100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>22131500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>21775800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>21715200</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4285,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,96 +4316,104 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6642000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6705500</v>
+      </c>
+      <c r="F57" s="3">
         <v>6694200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>6694200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>6458900</v>
       </c>
       <c r="G57" s="3">
         <v>6458900</v>
       </c>
       <c r="H57" s="3">
-        <v>4755900</v>
+        <v>6432700</v>
       </c>
       <c r="I57" s="3">
-        <v>4770900</v>
+        <v>6452900</v>
       </c>
       <c r="J57" s="3">
         <v>6545900</v>
       </c>
       <c r="K57" s="3">
+        <v>4770900</v>
+      </c>
+      <c r="L57" s="3">
+        <v>6545900</v>
+      </c>
+      <c r="M57" s="3">
         <v>6516400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5965300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5987600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5889200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5995500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5417700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5844200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5172800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5833600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5894300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5920800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4941100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5511200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>8151900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>8526300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>8369500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>8190400</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>833100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>841100</v>
+      </c>
+      <c r="F58" s="3">
         <v>782100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>782100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>754600</v>
       </c>
       <c r="G58" s="3">
         <v>754600</v>
@@ -4159,146 +4428,158 @@
         <v>703200</v>
       </c>
       <c r="K58" s="3">
+        <v>735200</v>
+      </c>
+      <c r="L58" s="3">
+        <v>703200</v>
+      </c>
+      <c r="M58" s="3">
         <v>2083800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>761100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1074700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1154700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1797900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>707200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1279300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1595700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>933200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>870100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>984900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>454400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>586900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>290900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>230900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>342400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>492500</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4237100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4277700</v>
+      </c>
+      <c r="F59" s="3">
         <v>5273300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>5273300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>5087900</v>
       </c>
       <c r="G59" s="3">
         <v>5087900</v>
       </c>
       <c r="H59" s="3">
-        <v>1392400</v>
+        <v>291900</v>
       </c>
       <c r="I59" s="3">
-        <v>1396800</v>
+        <v>292800</v>
       </c>
       <c r="J59" s="3">
         <v>388200</v>
       </c>
       <c r="K59" s="3">
+        <v>1396800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>388200</v>
+      </c>
+      <c r="M59" s="3">
         <v>6620000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6222500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6957300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>8478100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>7789600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>9146100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>8557800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>7247600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6802200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>7285400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7275100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>6172100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>5257900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>322200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>277800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>404300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>358200</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14367500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>14505000</v>
+      </c>
+      <c r="F60" s="3">
         <v>14877600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>14877600</v>
-      </c>
-      <c r="F60" s="3">
-        <v>14354600</v>
       </c>
       <c r="G60" s="3">
         <v>14354600</v>
@@ -4313,69 +4594,75 @@
         <v>14379100</v>
       </c>
       <c r="K60" s="3">
+        <v>14515500</v>
+      </c>
+      <c r="L60" s="3">
+        <v>14379100</v>
+      </c>
+      <c r="M60" s="3">
         <v>15220200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12948800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14019500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15522000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15583000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>15271000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>15681200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>14016200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>13568900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>14049800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>14180800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>11340300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>11062600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8765000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9035000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>9116100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>9041100</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7482600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7554200</v>
+      </c>
+      <c r="F61" s="3">
         <v>7908700</v>
-      </c>
-      <c r="E61" s="3">
-        <v>7908700</v>
-      </c>
-      <c r="F61" s="3">
-        <v>7630700</v>
       </c>
       <c r="G61" s="3">
         <v>7630700</v>
@@ -4390,135 +4677,147 @@
         <v>7639700</v>
       </c>
       <c r="K61" s="3">
+        <v>7565800</v>
+      </c>
+      <c r="L61" s="3">
+        <v>7639700</v>
+      </c>
+      <c r="M61" s="3">
         <v>7452000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8925600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8510900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7949300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7830400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8252700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7771100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7265400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>8113600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2184800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2042000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2693100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2731700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2856400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3018200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>3299900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>3443400</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>239100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>241400</v>
+      </c>
+      <c r="F62" s="3">
         <v>395600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>395600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>381700</v>
       </c>
       <c r="G62" s="3">
         <v>381700</v>
       </c>
       <c r="H62" s="3">
-        <v>298200</v>
+        <v>278000</v>
       </c>
       <c r="I62" s="3">
-        <v>299100</v>
+        <v>278900</v>
       </c>
       <c r="J62" s="3">
         <v>182300</v>
       </c>
       <c r="K62" s="3">
+        <v>299100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>182300</v>
+      </c>
+      <c r="M62" s="3">
         <v>2476100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2386900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1763600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>881800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1956000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2007400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2604400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2647300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2648400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>3663100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3223600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3039100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3586300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2214700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1977300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2066000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1966000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4893,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4976,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,19 +5059,25 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22648000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22864700</v>
+      </c>
+      <c r="F66" s="3">
         <v>23689200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>23689200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>22856500</v>
       </c>
       <c r="G66" s="3">
         <v>22856500</v>
@@ -4775,58 +5092,64 @@
         <v>23497200</v>
       </c>
       <c r="K66" s="3">
+        <v>23059800</v>
+      </c>
+      <c r="L66" s="3">
+        <v>23497200</v>
+      </c>
+      <c r="M66" s="3">
         <v>25148300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>24261300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>24294100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>24353100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>25369400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>25531000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>26056800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>23928900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>24330900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>19897700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>19446400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>17072500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>17380500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>13836100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>14030500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>14482100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>14450500</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5177,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5256,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5339,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5422,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,19 +5505,25 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5556000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5609100</v>
+      </c>
+      <c r="F72" s="3">
         <v>5268100</v>
-      </c>
-      <c r="E72" s="3">
-        <v>5268100</v>
-      </c>
-      <c r="F72" s="3">
-        <v>5082900</v>
       </c>
       <c r="G72" s="3">
         <v>5082900</v>
@@ -5189,58 +5538,64 @@
         <v>4407700</v>
       </c>
       <c r="K72" s="3">
+        <v>4102900</v>
+      </c>
+      <c r="L72" s="3">
+        <v>4407700</v>
+      </c>
+      <c r="M72" s="3">
         <v>7677700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>8331200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6689600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>6092500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>6555300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>6972700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6982000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6516600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>5988500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>7034400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6639700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6116600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5500900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>5484600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>5285100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5113100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5098600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5671,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5754,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,19 +5837,25 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8369800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8449900</v>
+      </c>
+      <c r="F76" s="3">
         <v>8692100</v>
-      </c>
-      <c r="E76" s="3">
-        <v>8692100</v>
-      </c>
-      <c r="F76" s="3">
-        <v>8386500</v>
       </c>
       <c r="G76" s="3">
         <v>8386500</v>
@@ -5497,58 +5870,64 @@
         <v>8958100</v>
       </c>
       <c r="K76" s="3">
+        <v>8705200</v>
+      </c>
+      <c r="L76" s="3">
+        <v>8958100</v>
+      </c>
+      <c r="M76" s="3">
         <v>10404400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11052700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9398000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8793100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9164100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9873500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9809800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9205300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>8751600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>10107000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>9816600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9076500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8395500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>8301900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>8101100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>7293700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>7264700</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,24 +6003,30 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45717</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45627</v>
+      </c>
+      <c r="F80" s="2">
         <v>45549</v>
-      </c>
-      <c r="E80" s="2">
-        <v>45549</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45457</v>
       </c>
       <c r="G80" s="2">
         <v>45457</v>
@@ -5656,58 +6041,64 @@
         <v>45185</v>
       </c>
       <c r="K80" s="2">
+        <v>45262</v>
+      </c>
+      <c r="L80" s="2">
+        <v>45185</v>
+      </c>
+      <c r="M80" s="2">
         <v>44821</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44625</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44457</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44261</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44093</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43897</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43729</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43533</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43365</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43169</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43001</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42805</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42637</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42441</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42273</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42077</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5732,59 +6123,65 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>374000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>377900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>496000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-31500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-233300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>225600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-60800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>65100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>137800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>184100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>220800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>92500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>373600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>256900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>341700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>234400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,16 +6209,18 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>230600</v>
+        <v>282400</v>
       </c>
       <c r="E83" s="3">
-        <v>231300</v>
+        <v>283300</v>
       </c>
       <c r="F83" s="3">
         <v>323700</v>
@@ -5839,58 +6238,64 @@
         <v>315200</v>
       </c>
       <c r="K83" s="3">
+        <v>245000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>315200</v>
+      </c>
+      <c r="M83" s="3">
         <v>852900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>736100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>864700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>771600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>842800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>746400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>827600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>687300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>830800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>503200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>512300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>397600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>422700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>360000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>401700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>343700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6371,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6454,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6537,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6620,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6703,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1294300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1306700</v>
+      </c>
+      <c r="F89" s="3">
         <v>418000</v>
-      </c>
-      <c r="E89" s="3">
-        <v>418000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>403300</v>
       </c>
       <c r="G89" s="3">
         <v>403300</v>
       </c>
       <c r="H89" s="3">
-        <v>430200</v>
+        <v>437800</v>
       </c>
       <c r="I89" s="3">
-        <v>431600</v>
+        <v>439200</v>
       </c>
       <c r="J89" s="3">
         <v>1065300</v>
       </c>
       <c r="K89" s="3">
+        <v>431600</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1065300</v>
+      </c>
+      <c r="M89" s="3">
         <v>2057500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>126000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1198000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1091800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1926700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>441000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1270600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>105300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1163800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>782800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1119400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>537600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>964400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>189100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>322200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>675500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>524100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,19 +6821,21 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-203900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-194500</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-194500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-187700</v>
       </c>
       <c r="G91" s="3">
         <v>-187700</v>
@@ -6407,58 +6850,64 @@
         <v>-645500</v>
       </c>
       <c r="K91" s="3">
+        <v>-215500</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-645500</v>
+      </c>
+      <c r="M91" s="3">
         <v>-308000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-375000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-319000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-294000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-301000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-374000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-265000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-282700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-286700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-380500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-399100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-431900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-396900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-373000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-469600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-583300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-771600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6983,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +7066,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-239700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-242000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-266800</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-266800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-257400</v>
       </c>
       <c r="G94" s="3">
         <v>-257400</v>
       </c>
       <c r="H94" s="3">
-        <v>-250800</v>
+        <v>-258400</v>
       </c>
       <c r="I94" s="3">
-        <v>-251600</v>
+        <v>-259200</v>
       </c>
       <c r="J94" s="3">
         <v>-652400</v>
       </c>
       <c r="K94" s="3">
+        <v>-251600</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-652400</v>
+      </c>
+      <c r="M94" s="3">
         <v>-379200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-482900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-368700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-380500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-335400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-422000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-115400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-308700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-259800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-261800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-393400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-394900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-583100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-113500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-408200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-454300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-730800</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,19 +7184,21 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>57800</v>
+      </c>
+      <c r="F96" s="3">
         <v>142600</v>
-      </c>
-      <c r="E96" s="3">
-        <v>142600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>137600</v>
       </c>
       <c r="G96" s="3">
         <v>137600</v>
@@ -6744,58 +7213,64 @@
         <v>133300</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>57700</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>133300</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-5200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-30200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-24800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-3500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-24400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-4100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-28300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-4000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-25900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>199600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-204800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-126400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7346,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7429,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,19 +7512,25 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-306400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-309400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-414000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-414000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-399500</v>
       </c>
       <c r="G100" s="3">
         <v>-399500</v>
@@ -7052,58 +7545,64 @@
         <v>49600</v>
       </c>
       <c r="K100" s="3">
+        <v>-229400</v>
+      </c>
+      <c r="L100" s="3">
+        <v>49600</v>
+      </c>
+      <c r="M100" s="3">
         <v>-682300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-452700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-883100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-681000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1006100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-618400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-724600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-912500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>19100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-365100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-281300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-327100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-233500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>66500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-385800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,11 +7627,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7179,19 +7678,25 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>748100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>755300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-262900</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-262900</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-253600</v>
       </c>
       <c r="G102" s="3">
         <v>-253600</v>
@@ -7206,54 +7711,60 @@
         <v>462600</v>
       </c>
       <c r="K102" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="L102" s="3">
+        <v>462600</v>
+      </c>
+      <c r="M102" s="3">
         <v>996000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-809600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-53800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>30200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>585300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-599400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>430600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-404600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-324500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>540100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>360900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-138700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>54300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-157800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-19600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-164600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-234400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -3100,10 +3100,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>914900</v>
+        <v>3494700</v>
       </c>
       <c r="E41" s="3">
-        <v>923600</v>
+        <v>3528100</v>
       </c>
       <c r="F41" s="3">
         <v>1194800</v>
@@ -3112,10 +3112,10 @@
         <v>1152800</v>
       </c>
       <c r="H41" s="3">
-        <v>1108100</v>
+        <v>2510600</v>
       </c>
       <c r="I41" s="3">
-        <v>1111600</v>
+        <v>2518500</v>
       </c>
       <c r="J41" s="3">
         <v>1076500</v>
@@ -3266,10 +3266,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>719800</v>
+        <v>476900</v>
       </c>
       <c r="E43" s="3">
-        <v>726700</v>
+        <v>481500</v>
       </c>
       <c r="F43" s="3">
         <v>897700</v>
@@ -3278,10 +3278,10 @@
         <v>866200</v>
       </c>
       <c r="H43" s="3">
-        <v>735400</v>
+        <v>495300</v>
       </c>
       <c r="I43" s="3">
-        <v>737700</v>
+        <v>496900</v>
       </c>
       <c r="J43" s="3">
         <v>829700</v>
@@ -3432,10 +3432,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3969100</v>
+        <v>3198900</v>
       </c>
       <c r="E45" s="3">
-        <v>4007100</v>
+        <v>3229500</v>
       </c>
       <c r="F45" s="3">
         <v>4112700</v>
@@ -3444,10 +3444,10 @@
         <v>3968100</v>
       </c>
       <c r="H45" s="3">
-        <v>44200</v>
+        <v>22700</v>
       </c>
       <c r="I45" s="3">
-        <v>44400</v>
+        <v>22800</v>
       </c>
       <c r="J45" s="3">
         <v>145100</v>
@@ -3610,10 +3610,10 @@
         <v>17800</v>
       </c>
       <c r="H47" s="3">
-        <v>2500</v>
+        <v>24000</v>
       </c>
       <c r="I47" s="3">
-        <v>2500</v>
+        <v>24100</v>
       </c>
       <c r="J47" s="3">
         <v>828500</v>
@@ -4013,10 +4013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1931700</v>
+        <v>1016800</v>
       </c>
       <c r="E52" s="3">
-        <v>1950200</v>
+        <v>1026500</v>
       </c>
       <c r="F52" s="3">
         <v>1008100</v>
@@ -4025,10 +4025,10 @@
         <v>972700</v>
       </c>
       <c r="H52" s="3">
-        <v>1919300</v>
+        <v>1094200</v>
       </c>
       <c r="I52" s="3">
-        <v>1925300</v>
+        <v>1097700</v>
       </c>
       <c r="J52" s="3">
         <v>1334500</v>
@@ -4324,10 +4324,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6642000</v>
+        <v>4911700</v>
       </c>
       <c r="E57" s="3">
-        <v>6705500</v>
+        <v>4958600</v>
       </c>
       <c r="F57" s="3">
         <v>6694200</v>
@@ -4336,10 +4336,10 @@
         <v>6458900</v>
       </c>
       <c r="H57" s="3">
-        <v>6432700</v>
+        <v>4755900</v>
       </c>
       <c r="I57" s="3">
-        <v>6452900</v>
+        <v>4770900</v>
       </c>
       <c r="J57" s="3">
         <v>6545900</v>
@@ -4490,10 +4490,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4237100</v>
+        <v>5337000</v>
       </c>
       <c r="E59" s="3">
-        <v>4277700</v>
+        <v>5388100</v>
       </c>
       <c r="F59" s="3">
         <v>5273300</v>
@@ -4502,10 +4502,10 @@
         <v>5087900</v>
       </c>
       <c r="H59" s="3">
-        <v>291900</v>
+        <v>1392400</v>
       </c>
       <c r="I59" s="3">
-        <v>292800</v>
+        <v>1396800</v>
       </c>
       <c r="J59" s="3">
         <v>388200</v>
@@ -4739,10 +4739,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>239100</v>
+        <v>241600</v>
       </c>
       <c r="E62" s="3">
-        <v>241400</v>
+        <v>243900</v>
       </c>
       <c r="F62" s="3">
         <v>395600</v>
@@ -4751,10 +4751,10 @@
         <v>381700</v>
       </c>
       <c r="H62" s="3">
-        <v>278000</v>
+        <v>299500</v>
       </c>
       <c r="I62" s="3">
-        <v>278900</v>
+        <v>300400</v>
       </c>
       <c r="J62" s="3">
         <v>182300</v>
@@ -6715,10 +6715,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1294300</v>
+        <v>822400</v>
       </c>
       <c r="E89" s="3">
-        <v>1306700</v>
+        <v>830300</v>
       </c>
       <c r="F89" s="3">
         <v>418000</v>
@@ -6727,10 +6727,10 @@
         <v>403300</v>
       </c>
       <c r="H89" s="3">
-        <v>437800</v>
+        <v>156000</v>
       </c>
       <c r="I89" s="3">
-        <v>439200</v>
+        <v>156500</v>
       </c>
       <c r="J89" s="3">
         <v>1065300</v>
@@ -7078,10 +7078,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-239700</v>
+        <v>232200</v>
       </c>
       <c r="E94" s="3">
-        <v>-242000</v>
+        <v>234400</v>
       </c>
       <c r="F94" s="3">
         <v>-266800</v>
@@ -7090,10 +7090,10 @@
         <v>-257400</v>
       </c>
       <c r="H94" s="3">
-        <v>-258400</v>
+        <v>23400</v>
       </c>
       <c r="I94" s="3">
-        <v>-259200</v>
+        <v>23400</v>
       </c>
       <c r="J94" s="3">
         <v>-652400</v>
